--- a/Banking_App_TestCases.xlsx
+++ b/Banking_App_TestCases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="602" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test plan" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,9 +11,9 @@
     <sheet name="UI Test Cases" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="API Test Cases" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Hybrid E2E Test Cases" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RTM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Defect Log" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Execution Report" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Defect Log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Execution Report" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="RTM" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -69,32 +69,79 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <b val="1"/>
       <color rgb="FF1F4E78"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <b val="1"/>
       <color rgb="FF333333"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -117,7 +164,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
@@ -127,7 +174,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -232,14 +279,74 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
         <bgColor rgb="001F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
     <fill>
@@ -248,26 +355,8 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-        <bgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -363,26 +452,6 @@
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
@@ -403,11 +472,90 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB7B7B7"/>
       </left>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -428,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -442,39 +590,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -482,9 +606,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -539,108 +660,168 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -921,135 +1102,135 @@
   <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="25" customWidth="1" style="17" min="1" max="1"/>
-    <col width="28" customWidth="1" style="17" min="2" max="2"/>
+    <col width="25" customWidth="1" style="9" min="1" max="1"/>
+    <col width="28" customWidth="1" style="9" min="2" max="2"/>
     <col width="85" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>PARABANK APPLICATION - MASTER TEST PLAN &amp; STRATEGY</t>
         </is>
       </c>
-      <c r="B1" s="54" t="n"/>
-      <c r="C1" s="55" t="n"/>
+      <c r="B1" s="84" t="n"/>
+      <c r="C1" s="85" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="79" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B2" s="41" t="inlineStr">
+      <c r="B2" s="79" t="inlineStr">
         <is>
           <t>Planning Parameter</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="80" t="inlineStr">
         <is>
           <t>Strategy &amp; Planning Details / Notes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28.05" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>1. DOCUMENT CONTROLS &amp; GENERAL OVERVIEW</t>
         </is>
       </c>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="55" t="n"/>
+      <c r="B3" s="84" t="n"/>
+      <c r="C3" s="85" t="n"/>
     </row>
     <row r="4" ht="19.95" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>Document Info</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>Target Application</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="83" t="inlineStr">
         <is>
           <t>ParaBank Banking Portal (https://parabank.parasoft.com)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="37.2" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="82" t="inlineStr">
         <is>
           <t>Document Info</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="82" t="inlineStr">
         <is>
           <t>Document Purpose</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="83" t="inlineStr">
         <is>
           <t>Defines the strategic testing planning, methodology, tools, environments, and scope that guided the design of the test scenarios (TS-01 to TS-18) and test cases contained in this repository workbook.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="19.95" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="82" t="inlineStr">
         <is>
           <t>Document Info</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="82" t="inlineStr">
         <is>
           <t>Version &amp; Date</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="83" t="inlineStr">
         <is>
           <t>v1.0 - June 20, 2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19.95" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="82" t="inlineStr">
         <is>
           <t>Document Info</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="82" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="83" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28.05" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>2. TEST OBJECTIVES &amp; SCOPE</t>
         </is>
       </c>
-      <c r="B8" s="54" t="n"/>
-      <c r="C8" s="55" t="n"/>
+      <c r="B8" s="84" t="n"/>
+      <c r="C8" s="85" t="n"/>
     </row>
     <row r="9" ht="136.2" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="82" t="inlineStr">
         <is>
           <t>Testing Scope</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="82" t="inlineStr">
         <is>
           <t>In-Scope Functions</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="83" t="inlineStr">
         <is>
           <t>1. User Management: Customer Registration &amp; Login validation via both UI (form) and API.
 2. Account Operations: Opening new accounts (Savings/Checking), retrieving customer account lists, and viewing specific account details.
@@ -1061,17 +1242,17 @@
       </c>
     </row>
     <row r="10" ht="64.05" customHeight="1">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Testing Scope</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="82" t="inlineStr">
         <is>
           <t>Out-of-Scope Functions</t>
         </is>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C10" s="83" t="inlineStr">
         <is>
           <t>1. Third-party integrations (external payment gateways, SMTP mail servers, etc.).
 2. Non-functional performance testing (load, stress, and spike testing) beyond basic response-time SLA validations.
@@ -1081,137 +1262,137 @@
       </c>
     </row>
     <row r="11" ht="28.05" customHeight="1">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>3. TEST METHODOLOGY &amp; TESTING TYPES</t>
         </is>
       </c>
-      <c r="B11" s="54" t="n"/>
-      <c r="C11" s="55" t="n"/>
+      <c r="B11" s="84" t="n"/>
+      <c r="C11" s="85" t="n"/>
     </row>
     <row r="12" ht="34.2" customHeight="1">
-      <c r="A12" s="42" t="inlineStr">
+      <c r="A12" s="82" t="inlineStr">
         <is>
           <t>Test Strategy</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="82" t="inlineStr">
         <is>
           <t>UI Functional Testing</t>
         </is>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="83" t="inlineStr">
         <is>
           <t>Validates frontend screens for usability, workflow flow correctness, and input validation. Tests are structured using the Page Object Model (POM) to ensure clean separation between UI locators and test script execution logic.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="31.8" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="82" t="inlineStr">
         <is>
           <t>Test Strategy</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="82" t="inlineStr">
         <is>
           <t>API Integration Testing</t>
         </is>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="83" t="inlineStr">
         <is>
           <t>Validates REST API endpoints directly for response code correctness, response body schemas, headers, and parameter handling. Assures that raw backend interfaces handle requests robustly independent of the UI.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32.4" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="82" t="inlineStr">
         <is>
           <t>Test Strategy</t>
         </is>
       </c>
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="82" t="inlineStr">
         <is>
           <t>Hybrid (End-to-End) Testing</t>
         </is>
       </c>
-      <c r="C14" s="40" t="inlineStr">
+      <c r="C14" s="83" t="inlineStr">
         <is>
           <t>Performs cross-layer checks where a process is initiated on the UI layer (e.g. Account Creation) and the resulting system state is verified by calling the corresponding REST API. Ensures complete data consistency across layers.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="31.2" customHeight="1">
-      <c r="A15" s="42" t="inlineStr">
+      <c r="A15" s="82" t="inlineStr">
         <is>
           <t>Test Strategy</t>
         </is>
       </c>
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="82" t="inlineStr">
         <is>
           <t>API Performance SLAs</t>
         </is>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="83" t="inlineStr">
         <is>
           <t>Assesses system latency under typical loads by timing critical endpoints: Login API must respond within 2.0 seconds; single GET operations and multi-request API call chains must complete within 5.0 seconds.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34.2" customHeight="1">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="82" t="inlineStr">
         <is>
           <t>Test Strategy</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="82" t="inlineStr">
         <is>
           <t>Negative &amp; Boundary Testing</t>
         </is>
       </c>
-      <c r="C16" s="40" t="inlineStr">
+      <c r="C16" s="83" t="inlineStr">
         <is>
           <t>Verifies system resilience under unexpected or faulty conditions. Includes: registration with mismatched passwords, transfers exceeding available balances, negative transfer amounts, requests using invalid or nonexistent customer/account IDs, and handling of mock endpoint failures.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28.05" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>4. REQUIREMENTS TRACEABILITY &amp; MAPPING STRATEGY</t>
         </is>
       </c>
-      <c r="B17" s="54" t="n"/>
-      <c r="C17" s="55" t="n"/>
+      <c r="B17" s="84" t="n"/>
+      <c r="C17" s="85" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="82" t="inlineStr">
         <is>
           <t>Traceability (RTM)</t>
         </is>
       </c>
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="82" t="inlineStr">
         <is>
           <t>Mapping Rationale</t>
         </is>
       </c>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C18" s="83" t="inlineStr">
         <is>
           <t>All test cases are derived from the 9 core Functional Requirements (FR-01 to FR-09). To maintain structured coverage, each Functional Requirement maps to exactly 2 Test Scenarios (one positive, one negative/validation), and each Functional Requirement has exactly 6 test cases associated with it (yielding a balanced distribution of 54 test cases total).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="42" t="inlineStr">
+      <c r="A19" s="82" t="inlineStr">
         <is>
           <t>Traceability (RTM)</t>
         </is>
       </c>
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="82" t="inlineStr">
         <is>
           <t>Functional Coverage</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="83" t="inlineStr">
         <is>
           <t>• FR-01/FR-08: UI Registration, login, page messages, savings accounts.
 • FR-02/FR-03/FR-04: API-based accounts, customer details lookup, and Hybrid UI/API cross-validation.
@@ -1220,137 +1401,137 @@
       </c>
     </row>
     <row r="20" ht="28.05" customHeight="1">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>5. TOOLING &amp; TEST ENVIRONMENT CONFIGURATION</t>
         </is>
       </c>
-      <c r="B20" s="54" t="n"/>
-      <c r="C20" s="55" t="n"/>
+      <c r="B20" s="84" t="n"/>
+      <c r="C20" s="85" t="n"/>
     </row>
     <row r="21" ht="19.95" customHeight="1">
-      <c r="A21" s="42" t="inlineStr">
+      <c r="A21" s="82" t="inlineStr">
         <is>
           <t>Tooling &amp; Setup</t>
         </is>
       </c>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="82" t="inlineStr">
         <is>
           <t>Test Automation Framework</t>
         </is>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="83" t="inlineStr">
         <is>
           <t>Robot Framework (Python-based keyword-driven testing framework)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19.95" customHeight="1">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="A22" s="82" t="inlineStr">
         <is>
           <t>Tooling &amp; Setup</t>
         </is>
       </c>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="82" t="inlineStr">
         <is>
           <t>Core UI Libraries</t>
         </is>
       </c>
-      <c r="C22" s="40" t="inlineStr">
+      <c r="C22" s="83" t="inlineStr">
         <is>
           <t>SeleniumLibrary (driving Chrome/Firefox headless browsers for UI flows)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19.95" customHeight="1">
-      <c r="A23" s="42" t="inlineStr">
+      <c r="A23" s="82" t="inlineStr">
         <is>
           <t>Tooling &amp; Setup</t>
         </is>
       </c>
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="82" t="inlineStr">
         <is>
           <t>Core API Libraries</t>
         </is>
       </c>
-      <c r="C23" s="40" t="inlineStr">
+      <c r="C23" s="83" t="inlineStr">
         <is>
           <t>RequestsLibrary (handling HTTP GET/POST calls and assertion of payloads)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19.95" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="82" t="inlineStr">
         <is>
           <t>Tooling &amp; Setup</t>
         </is>
       </c>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="82" t="inlineStr">
         <is>
           <t>Data-Driven Libraries</t>
         </is>
       </c>
-      <c r="C24" s="40" t="inlineStr">
+      <c r="C24" s="83" t="inlineStr">
         <is>
           <t>DataDriver with Excel integration (XLS/XLSX) to feed multiple test inputs dynamically</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19.95" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="82" t="inlineStr">
         <is>
           <t>Tooling &amp; Setup</t>
         </is>
       </c>
-      <c r="B25" s="42" t="inlineStr">
+      <c r="B25" s="82" t="inlineStr">
         <is>
           <t>Parallel Execution</t>
         </is>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="83" t="inlineStr">
         <is>
           <t>Pabot library used to split and execute test suites in parallel, minimizing test suite execution time</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33" customHeight="1">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="A26" s="82" t="inlineStr">
         <is>
           <t>Tooling &amp; Setup</t>
         </is>
       </c>
-      <c r="B26" s="42" t="inlineStr">
+      <c r="B26" s="82" t="inlineStr">
         <is>
           <t>CI/CD Integration</t>
         </is>
       </c>
-      <c r="C26" s="40" t="inlineStr">
+      <c r="C26" s="83" t="inlineStr">
         <is>
           <t>Jenkins Pipeline integration (Jenkinsfile) executing tests automatically upon code commits, producing Allure and Robot Framework HTML test reports</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28.05" customHeight="1">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="81" t="inlineStr">
         <is>
           <t>6. DEFECT MANAGEMENT &amp; CLASSIFICATION</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="55" t="n"/>
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="85" t="n"/>
     </row>
     <row r="28" ht="64.05" customHeight="1">
-      <c r="A28" s="42" t="inlineStr">
+      <c r="A28" s="82" t="inlineStr">
         <is>
           <t>Defect Management</t>
         </is>
       </c>
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="82" t="inlineStr">
         <is>
           <t>Severity Definitions</t>
         </is>
       </c>
-      <c r="C28" s="40" t="inlineStr">
+      <c r="C28" s="83" t="inlineStr">
         <is>
           <t>• Critical: App crash, data corruption, or blocker with no workaround.
 • High: Core feature broken with no functional workaround.
@@ -1360,17 +1541,17 @@
       </c>
     </row>
     <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="42" t="inlineStr">
+      <c r="A29" s="82" t="inlineStr">
         <is>
           <t>Defect Management</t>
         </is>
       </c>
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B29" s="82" t="inlineStr">
         <is>
           <t>Priority Definitions</t>
         </is>
       </c>
-      <c r="C29" s="40" t="inlineStr">
+      <c r="C29" s="83" t="inlineStr">
         <is>
           <t>• P1: Resolve immediately (blocks regression testing or primary customer journeys).
 • P2: Resolve prior to release candidate staging.
@@ -1398,539 +1579,569 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.2"/>
   <cols>
-    <col width="17.6640625" customWidth="1" min="1" max="1"/>
-    <col width="16.109375" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="6"/>
+    <col width="17.6640625" customWidth="1" style="74" min="1" max="1"/>
+    <col width="16.109375" customWidth="1" style="74" min="2" max="2"/>
+    <col width="34" customWidth="1" style="74" min="3" max="3"/>
+    <col width="48" customWidth="1" style="74" min="4" max="4"/>
+    <col width="10" customWidth="1" style="74" min="5" max="6"/>
+    <col width="8.6640625" customWidth="1" style="74" min="7" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="73" t="inlineStr">
         <is>
           <t>Scenario ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="73" t="inlineStr">
         <is>
           <t>Scenario Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="73" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="73" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="73" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2" ht="27.6" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>FR-01</t>
         </is>
       </c>
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>TS-01</t>
         </is>
       </c>
-      <c r="C2" s="49" t="inlineStr">
+      <c r="C2" s="37" t="inlineStr">
         <is>
           <t>Successful account creation</t>
         </is>
       </c>
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="37" t="inlineStr">
         <is>
           <t>Verify successful account creation for create new account via ui.</t>
         </is>
       </c>
-      <c r="E2" s="49" t="inlineStr">
+      <c r="E2" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="3" ht="27.6" customHeight="1">
-      <c r="A3" s="48" t="n"/>
-      <c r="B3" s="49" t="inlineStr">
+      <c r="A3" s="35" t="n"/>
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>TS-02</t>
         </is>
       </c>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>Mandatory and field-level validation</t>
         </is>
       </c>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="D3" s="37" t="inlineStr">
         <is>
           <t>Verify mandatory and field-level validation for create new account via ui.</t>
         </is>
       </c>
-      <c r="E3" s="49" t="inlineStr">
+      <c r="E3" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="4" ht="27.6" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>FR-02</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>TS-03</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>Successful GET accounts retrieval</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Verify successful GET accounts retrieval for get accounts list via api.</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="5" ht="27.6" customHeight="1">
-      <c r="A5" s="48" t="n"/>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="A5" s="35" t="n"/>
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>TS-04</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>API access and response validation</t>
         </is>
       </c>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Verify API access and response validation for get accounts list via api.</t>
         </is>
       </c>
-      <c r="E5" s="49" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="6" ht="27.6" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>FR-03</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>TS-05</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>UI-created account is present in API</t>
         </is>
       </c>
-      <c r="D6" s="49" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Verify UI-created account is present in API for validate new account exists in api.</t>
         </is>
       </c>
-      <c r="E6" s="49" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="7" ht="27.6" customHeight="1">
-      <c r="A7" s="48" t="n"/>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>TS-06</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Account lookup/search validation</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Verify account lookup/search validation for validate new account exists in api.</t>
         </is>
       </c>
-      <c r="E7" s="49" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="8" ht="27.6" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>FR-04</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>TS-07</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Type and details match UI</t>
         </is>
       </c>
-      <c r="D8" s="49" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Verify type and details match UI for validate account type and details in api.</t>
         </is>
       </c>
-      <c r="E8" s="49" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="9" ht="27.6" customHeight="1">
-      <c r="A9" s="48" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>TS-08</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Performance and Response time</t>
         </is>
       </c>
-      <c r="D9" s="49" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Verify performance of API and response time of the session</t>
         </is>
       </c>
-      <c r="E9" s="49" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28.8" customHeight="1">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>FR-05</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>TS-09</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>Successful transfer flow</t>
         </is>
       </c>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Verify successful transfer flow for transfer funds via ui.</t>
         </is>
       </c>
-      <c r="E10" s="49" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11" ht="27.6" customHeight="1">
-      <c r="A11" s="48" t="n"/>
-      <c r="B11" s="49" t="inlineStr">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>TS-10</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Transfer input and business-rule validation</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Verify transfer input and business-rule validation for transfer funds via ui.</t>
         </is>
       </c>
-      <c r="E11" s="49" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="12" ht="27.6" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>FR-06</t>
         </is>
       </c>
-      <c r="B12" s="49" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>TS-11</t>
         </is>
       </c>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Balance consistency on repeated transfers</t>
         </is>
       </c>
-      <c r="D12" s="49" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Verify balance consistency on repeated transfers for validate updated balances using api.</t>
         </is>
       </c>
-      <c r="E12" s="49" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="13" hidden="1" ht="27.6" customHeight="1">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>FR-07</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>TS-13</t>
         </is>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Before/after balance delta validation</t>
         </is>
       </c>
-      <c r="D13" s="49" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Verify before/after balance delta validation for validate transfer applied correctly (before/after values).</t>
         </is>
       </c>
-      <c r="E13" s="49" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="F13" s="49" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
     </row>
     <row r="14" ht="27.6" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>FR-07</t>
         </is>
       </c>
-      <c r="B14" s="49" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>TS-14</t>
         </is>
       </c>
-      <c r="C14" s="49" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Multi-transfer correctness</t>
         </is>
       </c>
-      <c r="D14" s="49" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Verify multi-transfer correctness for validate transfer applied correctly (before/after values).</t>
         </is>
       </c>
-      <c r="E14" s="49" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="15" ht="27.6" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="66" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>TS-15</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Success and confirmation message validation</t>
         </is>
       </c>
-      <c r="D15" s="49" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Verify success and confirmation message validation for validate ui messages (success, confirmation).</t>
         </is>
       </c>
-      <c r="E15" s="49" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="16" ht="27.6" customHeight="1">
-      <c r="A16" s="48" t="n"/>
-      <c r="B16" s="49" t="inlineStr">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>TS-16</t>
         </is>
       </c>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>Message behavior on failure or navigation</t>
         </is>
       </c>
-      <c r="D16" s="49" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Verify message behavior on failure or navigation for validate ui messages (success, confirmation).</t>
         </is>
       </c>
-      <c r="E16" s="49" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="17" ht="27.6" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="69" t="inlineStr">
         <is>
           <t>FR-09</t>
         </is>
       </c>
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>TS-17</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Mandatory and invalid input negatives</t>
         </is>
       </c>
-      <c r="D17" s="49" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Verify mandatory and invalid input negatives for validate negative scenarios.</t>
         </is>
       </c>
-      <c r="E17" s="49" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="65" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
     </row>
+    <row r="18" ht="26.4" customHeight="1">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="71" t="inlineStr">
+        <is>
+          <t>TS-18</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>Business-rule and system negatives</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>Verify that call account/balance endpoint results in API failure handled correctly.</t>
+        </is>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F18" s="72" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A2:A3"/>
@@ -1958,10 +2169,10 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="44.33203125" customWidth="1" style="11" min="8" max="8"/>
+    <col width="44.33203125" customWidth="1" style="6" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" style="16" min="10" max="10"/>
-    <col width="23.77734375" customWidth="1" style="16" min="11" max="11"/>
+    <col width="40" customWidth="1" style="8" min="10" max="10"/>
+    <col width="23.77734375" customWidth="1" style="8" min="11" max="11"/>
     <col width="20.88671875" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
@@ -1971,124 +2182,124 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Scenario ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Scenario Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="60" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="60" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Automation Status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Manual Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>FR Mapping</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
     </row>
     <row r="2" ht="55.2" customHeight="1">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS01-01</t>
         </is>
       </c>
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>TS-01</t>
         </is>
       </c>
-      <c r="C2" s="49" t="inlineStr">
+      <c r="C2" s="37" t="inlineStr">
         <is>
           <t>Successful account registration</t>
         </is>
       </c>
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="37" t="inlineStr">
         <is>
           <t>Register new account</t>
         </is>
       </c>
-      <c r="E2" s="49" t="inlineStr">
+      <c r="E2" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F2" s="49" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Verify that open account page results in account is created, success message appears, new account number/ID is shown.</t>
         </is>
       </c>
-      <c r="G2" s="49" t="inlineStr">
+      <c r="G2" s="37" t="inlineStr">
         <is>
           <t>Open Account page available.</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="61" t="inlineStr">
         <is>
           <t>1. Navigate to https://parabank.parasoft.com
 2. Click "register"
@@ -2096,81 +2307,81 @@
 4. Click "Register"</t>
         </is>
       </c>
-      <c r="I2" s="49" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
         <is>
           <t>Account is created, success message appears, new account number/ID is shown.</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="61" t="inlineStr">
         <is>
           <t>Account registration successful, account is valid for 30 mins</t>
         </is>
       </c>
-      <c r="K2" s="13" t="inlineStr">
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="L2" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M2" s="49" t="inlineStr">
+      <c r="M2" s="37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="N2" s="49" t="inlineStr">
+      <c r="N2" s="37" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="O2" s="49" t="inlineStr">
+      <c r="O2" s="37" t="inlineStr">
         <is>
           <t>FR-01</t>
         </is>
       </c>
-      <c r="P2" s="49" t="inlineStr">
+      <c r="P2" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @smoke</t>
         </is>
       </c>
-      <c r="R2" s="12" t="n"/>
+      <c r="R2" s="7" t="n"/>
     </row>
     <row r="3" ht="55.2" customHeight="1">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS01-02</t>
         </is>
       </c>
-      <c r="B3" s="50" t="n"/>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>Successful account login</t>
         </is>
       </c>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="D3" s="37" t="inlineStr">
         <is>
           <t>Login with valid credentials</t>
         </is>
       </c>
-      <c r="E3" s="49" t="inlineStr">
+      <c r="E3" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F3" s="49" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Verify that a registered user can login successfully with correct username and password.</t>
         </is>
       </c>
-      <c r="G3" s="49" t="inlineStr">
+      <c r="G3" s="37" t="inlineStr">
         <is>
           <t>Same as above.</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="61" t="inlineStr">
         <is>
           <t>1. Navigate to https://parabank.parasoft.com
 2. Enter valid username (e.g. john)
@@ -2178,80 +2389,80 @@
 4. Click "Log In"</t>
         </is>
       </c>
-      <c r="I3" s="49" t="inlineStr">
+      <c r="I3" s="37" t="inlineStr">
         <is>
           <t>Account created successfully and displayed in UI.</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="61" t="inlineStr">
         <is>
           <t>Account login is successful with valid credentials</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M3" s="49" t="inlineStr">
+      <c r="M3" s="37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="N3" s="49" t="inlineStr">
+      <c r="N3" s="37" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="O3" s="49" t="inlineStr">
+      <c r="O3" s="37" t="inlineStr">
         <is>
           <t>FR-01</t>
         </is>
       </c>
-      <c r="P3" s="49" t="inlineStr">
+      <c r="P3" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @smoke</t>
         </is>
       </c>
     </row>
     <row r="4" ht="55.2" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS01-03</t>
         </is>
       </c>
-      <c r="B4" s="50" t="n"/>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="B4" s="36" t="n"/>
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>Unsuccessful account login</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Login with invalid credentials</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Verify that a unregistered user cannot login successfully with incorrect username and password.</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="37" t="inlineStr">
         <is>
           <t>Same as above.</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="61" t="inlineStr">
         <is>
           <t>1. Navigate to https://parabank.parasoft.com
 2. Enter valid username (e.g. mem)
@@ -2259,80 +2470,80 @@
 4. Click "Log In"</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
         <is>
           <t>Results in unsuccessful login with error</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="61" t="inlineStr">
         <is>
           <t>Invalid credentials not found; login unsuccessful</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="N4" s="49" t="inlineStr">
+      <c r="N4" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O4" s="49" t="inlineStr">
+      <c r="O4" s="37" t="inlineStr">
         <is>
           <t>FR-01</t>
         </is>
       </c>
-      <c r="P4" s="49" t="inlineStr">
+      <c r="P4" s="37" t="inlineStr">
         <is>
           <t>@ui @regression</t>
         </is>
       </c>
     </row>
     <row r="5" ht="96.59999999999999" customHeight="1">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS01-04</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n"/>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>Open savings account</t>
         </is>
       </c>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Savings account</t>
         </is>
       </c>
-      <c r="E5" s="49" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F5" s="49" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Verify that user can open a savings account and fetch the new account number</t>
         </is>
       </c>
-      <c r="G5" s="49" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>Same as above.</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="61" t="inlineStr">
         <is>
           <t>1. Navigate to https://parabank.parasoft.com
 2. Enter valid username (e.g. mem)
@@ -2342,247 +2553,247 @@
 6. Choose an existing account and click on "Open New Account".</t>
         </is>
       </c>
-      <c r="I5" s="49" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>Results in new savings account opening</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="J5" s="61" t="inlineStr">
         <is>
           <t>New savings account opened for the registered user</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L5" s="13" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M5" s="49" t="inlineStr">
+      <c r="M5" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="N5" s="49" t="inlineStr">
+      <c r="N5" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O5" s="49" t="inlineStr">
+      <c r="O5" s="37" t="inlineStr">
         <is>
           <t>FR-01</t>
         </is>
       </c>
-      <c r="P5" s="49" t="inlineStr">
+      <c r="P5" s="37" t="inlineStr">
         <is>
           <t>@ui @regression</t>
         </is>
       </c>
     </row>
     <row r="6" ht="41.4" customHeight="1">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS02-01</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>TS-02</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>Mandatory and field-level validation</t>
         </is>
       </c>
-      <c r="D6" s="49" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Account Creation with Blank Username</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F6" s="49" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Verify that leave username blank results in mandatory field error shown for account name.</t>
         </is>
       </c>
-      <c r="G6" s="49" t="inlineStr">
+      <c r="G6" s="37" t="inlineStr">
         <is>
           <t>Page open.</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="61" t="inlineStr">
         <is>
           <t>1. Leave username blank
 2. Submit.</t>
         </is>
       </c>
-      <c r="I6" s="49" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
         <is>
           <t>Mandatory field error shown for username.</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="J6" s="61" t="inlineStr">
         <is>
           <t>Account registration without username unsuccessful</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M6" s="49" t="inlineStr">
+      <c r="M6" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="N6" s="49" t="inlineStr">
+      <c r="N6" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O6" s="49" t="inlineStr">
+      <c r="O6" s="37" t="inlineStr">
         <is>
           <t>FR-01</t>
         </is>
       </c>
-      <c r="P6" s="49" t="inlineStr">
+      <c r="P6" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @negative @smoke</t>
         </is>
       </c>
     </row>
     <row r="7" ht="41.4" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS02-03</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n"/>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Mandatory and field-level validation</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Account Creation with mismatched password</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F7" s="49" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Verify that enter mismatch password results in mismatch error</t>
         </is>
       </c>
-      <c r="G7" s="49" t="inlineStr">
+      <c r="G7" s="37" t="inlineStr">
         <is>
           <t>Page open.</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="61" t="inlineStr">
         <is>
           <t>1. Enter required credentials.
 2. Enter mismatched password
 3. Submit.</t>
         </is>
       </c>
-      <c r="I7" s="49" t="inlineStr">
+      <c r="I7" s="37" t="inlineStr">
         <is>
           <t>Mismatched password is rejected and error message displayed.</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J7" s="61" t="inlineStr">
         <is>
           <t>Password did not match error</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M7" s="49" t="inlineStr">
+      <c r="M7" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="N7" s="49" t="inlineStr">
+      <c r="N7" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O7" s="49" t="inlineStr">
+      <c r="O7" s="37" t="inlineStr">
         <is>
           <t>FR-01</t>
         </is>
       </c>
-      <c r="P7" s="49" t="inlineStr">
+      <c r="P7" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @negative @boundary</t>
         </is>
       </c>
     </row>
     <row r="8" ht="69" customHeight="1">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS09-01</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>TS-09</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Successful transfer flow</t>
         </is>
       </c>
-      <c r="D8" s="49" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Transfer Valid Amount Between Own Accounts</t>
         </is>
       </c>
-      <c r="E8" s="49" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F8" s="49" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Verify funds can be transferred successfully between two accounts.</t>
         </is>
       </c>
-      <c r="G8" s="49" t="inlineStr">
+      <c r="G8" s="37" t="inlineStr">
         <is>
           <t>User is logged in. At least two accounts exist. Source account has sufficient balance.</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="61" t="inlineStr">
         <is>
           <t>1. Click "Transfer Funds"
 2. Enter Amount: 100
@@ -2591,606 +2802,606 @@
 5. Click "Transfer"</t>
         </is>
       </c>
-      <c r="I8" s="49" t="inlineStr">
+      <c r="I8" s="37" t="inlineStr">
         <is>
           <t>Transfer completes successfully with confirmation.</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="J8" s="61" t="inlineStr">
         <is>
           <t>1. Funds transferred successfully. Message 'Transfer Complete!' displayed with the correct amount.
 2. Transfer happens only to self account (Saving and/or Checking type account)</t>
         </is>
       </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M8" s="49" t="inlineStr">
+      <c r="M8" s="37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="N8" s="49" t="inlineStr">
+      <c r="N8" s="37" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="O8" s="49" t="inlineStr">
+      <c r="O8" s="37" t="inlineStr">
         <is>
           <t>FR-05</t>
         </is>
       </c>
-      <c r="P8" s="49" t="inlineStr">
+      <c r="P8" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @smoke</t>
         </is>
       </c>
     </row>
     <row r="9" ht="27.6" customHeight="1">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS09-02</t>
         </is>
       </c>
-      <c r="B9" s="50" t="n"/>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Successful transfer flow</t>
         </is>
       </c>
-      <c r="D9" s="49" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Transfer Minimum Valid Amount</t>
         </is>
       </c>
-      <c r="E9" s="49" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F9" s="49" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Verify that transfer minimum valid amount results in transfer succeeds.</t>
         </is>
       </c>
-      <c r="G9" s="49" t="inlineStr">
+      <c r="G9" s="37" t="inlineStr">
         <is>
           <t>Same as above.</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="61" t="inlineStr">
         <is>
           <t>Transfer minimum valid amount.</t>
         </is>
       </c>
-      <c r="I9" s="49" t="inlineStr">
+      <c r="I9" s="37" t="inlineStr">
         <is>
           <t>Transfer succeeds.</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J9" s="61" t="inlineStr">
         <is>
           <t>Transaction is successful even if typed negative values</t>
         </is>
       </c>
-      <c r="K9" s="14" t="inlineStr">
+      <c r="K9" s="63" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="L9" s="63" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="M9" s="49" t="inlineStr">
+      <c r="M9" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="N9" s="49" t="inlineStr">
+      <c r="N9" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O9" s="49" t="inlineStr">
+      <c r="O9" s="37" t="inlineStr">
         <is>
           <t>FR-05</t>
         </is>
       </c>
-      <c r="P9" s="49" t="inlineStr">
+      <c r="P9" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @boundary</t>
         </is>
       </c>
     </row>
     <row r="10" ht="41.4" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS09-03</t>
         </is>
       </c>
-      <c r="B10" s="48" t="n"/>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>Successful transfer flow</t>
         </is>
       </c>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Transfer to a Valid Destination Account</t>
         </is>
       </c>
-      <c r="E10" s="49" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F10" s="49" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Verify that transfer to a valid different destination account results in transaction is accepted and recorded.</t>
         </is>
       </c>
-      <c r="G10" s="49" t="inlineStr">
+      <c r="G10" s="37" t="inlineStr">
         <is>
           <t>Same as above.</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="61" t="inlineStr">
         <is>
           <t>Transfer to a valid different destination account.</t>
         </is>
       </c>
-      <c r="I10" s="49" t="inlineStr">
+      <c r="I10" s="37" t="inlineStr">
         <is>
           <t>Transaction is accepted and recorded.</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J10" s="61" t="inlineStr">
         <is>
           <t>Successful transaction transfer to valid different destination account</t>
         </is>
       </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M10" s="49" t="inlineStr">
+      <c r="M10" s="37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="N10" s="49" t="inlineStr">
+      <c r="N10" s="37" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="O10" s="49" t="inlineStr">
+      <c r="O10" s="37" t="inlineStr">
         <is>
           <t>FR-05</t>
         </is>
       </c>
-      <c r="P10" s="49" t="inlineStr">
+      <c r="P10" s="37" t="inlineStr">
         <is>
           <t>@ui @regression</t>
         </is>
       </c>
     </row>
     <row r="11" ht="41.4" customHeight="1">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS10-01</t>
         </is>
       </c>
-      <c r="B11" s="51" t="inlineStr">
+      <c r="B11" s="57" t="inlineStr">
         <is>
           <t>TS-10</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Transfer input and business-rule validation</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Transfer Amount Exceeding Source Balance</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F11" s="49" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Verify that enter amount greater than source balance results in transfer is blocked with insufficient funds message.</t>
         </is>
       </c>
-      <c r="G11" s="49" t="inlineStr">
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>Page open.</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="61" t="inlineStr">
         <is>
           <t>Enter amount greater than source balance.</t>
         </is>
       </c>
-      <c r="I11" s="49" t="inlineStr">
+      <c r="I11" s="37" t="inlineStr">
         <is>
           <t>Transfer is blocked with insufficient funds message.</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="J11" s="61" t="inlineStr">
         <is>
           <t>Transaction successful even when exceeding amount is applied</t>
         </is>
       </c>
-      <c r="K11" s="14" t="inlineStr">
+      <c r="K11" s="63" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="L11" s="63" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="M11" s="49" t="inlineStr">
+      <c r="M11" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="N11" s="49" t="inlineStr">
+      <c r="N11" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O11" s="49" t="inlineStr">
+      <c r="O11" s="37" t="inlineStr">
         <is>
           <t>FR-05</t>
         </is>
       </c>
-      <c r="P11" s="49" t="inlineStr">
+      <c r="P11" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @negative @smoke</t>
         </is>
       </c>
     </row>
     <row r="12" ht="41.4" customHeight="1">
-      <c r="A12" s="49" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS10-02</t>
         </is>
       </c>
-      <c r="B12" s="50" t="n"/>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Transfer input and business-rule validation</t>
         </is>
       </c>
-      <c r="D12" s="49" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Transfer with Invalid Destination Account Number</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F12" s="49" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Verify that enter invalid destination account number results in validation error shown and transfer not executed.</t>
         </is>
       </c>
-      <c r="G12" s="49" t="inlineStr">
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>Page open.</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="61" t="inlineStr">
         <is>
           <t>Enter invalid destination account number.</t>
         </is>
       </c>
-      <c r="I12" s="49" t="inlineStr">
+      <c r="I12" s="37" t="inlineStr">
         <is>
           <t>Validation error shown and transfer not executed.</t>
         </is>
       </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="J12" s="61" t="inlineStr">
         <is>
           <t>Invalid destination account number is not visible i.e. the destination account does not exist</t>
         </is>
       </c>
-      <c r="K12" s="13" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M12" s="49" t="inlineStr">
+      <c r="M12" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="N12" s="49" t="inlineStr">
+      <c r="N12" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O12" s="49" t="inlineStr">
+      <c r="O12" s="37" t="inlineStr">
         <is>
           <t>FR-05</t>
         </is>
       </c>
-      <c r="P12" s="49" t="inlineStr">
+      <c r="P12" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @negative</t>
         </is>
       </c>
     </row>
     <row r="13" ht="27.6" customHeight="1">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS15-01</t>
         </is>
       </c>
-      <c r="B13" s="51" t="inlineStr">
+      <c r="B13" s="57" t="inlineStr">
         <is>
           <t>TS-15</t>
         </is>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Success and confirmation message validation</t>
         </is>
       </c>
-      <c r="D13" s="49" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Verify Success Message on Account Creation</t>
         </is>
       </c>
-      <c r="E13" s="49" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F13" s="49" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Verify that create account with valid data results in success message is displayed.</t>
         </is>
       </c>
-      <c r="G13" s="49" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>Account creation page open.</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="61" t="inlineStr">
         <is>
           <t>Create account with valid data.</t>
         </is>
       </c>
-      <c r="I13" s="49" t="inlineStr">
+      <c r="I13" s="37" t="inlineStr">
         <is>
           <t>Success message is displayed.</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="J13" s="61" t="inlineStr">
         <is>
           <t>Validation message is visible after successful account creation</t>
         </is>
       </c>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M13" s="49" t="inlineStr">
+      <c r="M13" s="37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="N13" s="49" t="inlineStr">
+      <c r="N13" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O13" s="49" t="inlineStr">
+      <c r="O13" s="37" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="P13" s="49" t="inlineStr">
+      <c r="P13" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @smoke</t>
         </is>
       </c>
     </row>
     <row r="14" ht="27.6" customHeight="1">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS16-01</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>TS-16</t>
         </is>
       </c>
-      <c r="C14" s="49" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Message behavior on failure or navigation</t>
         </is>
       </c>
-      <c r="D14" s="49" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Verify Error Message Shown Instead of Confirmation</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F14" s="49" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Verify that failed message displayed on entering non-numeric values</t>
         </is>
       </c>
-      <c r="G14" s="49" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>Failed transfer attempt.</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="61" t="inlineStr">
         <is>
           <t>Inspect UI after error.</t>
         </is>
       </c>
-      <c r="I14" s="49" t="inlineStr">
+      <c r="I14" s="37" t="inlineStr">
         <is>
           <t>Error message shown instead of confirmation.</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J14" s="61" t="inlineStr">
         <is>
           <t>Error message displayed on entering non-numeric value</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="13" t="inlineStr">
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M14" s="49" t="inlineStr">
+      <c r="M14" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="N14" s="49" t="inlineStr">
+      <c r="N14" s="37" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O14" s="49" t="inlineStr">
+      <c r="O14" s="37" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="P14" s="49" t="inlineStr">
+      <c r="P14" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @negative</t>
         </is>
       </c>
     </row>
     <row r="15" ht="69" customHeight="1">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>TC-UI-TS17-01</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>TS-17</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Mandatory and invalid input negatives</t>
         </is>
       </c>
-      <c r="D15" s="49" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Submit Form with Boundary-Breaking Values</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F15" s="49" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Verify that submit out-of-range or boundary-breaking values results in boundary validation message shown.</t>
         </is>
       </c>
-      <c r="G15" s="49" t="inlineStr">
+      <c r="G15" s="37" t="inlineStr">
         <is>
           <t>Page open.</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="61" t="inlineStr">
         <is>
           <t>Submit out-of-range or boundary-breaking values.</t>
         </is>
       </c>
-      <c r="I15" s="49" t="inlineStr">
+      <c r="I15" s="37" t="inlineStr">
         <is>
           <t>Boundary validation message shown.</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J15" s="61" t="inlineStr">
         <is>
           <t>1. No boundary value or out-of-range values are present for input fields of registration
 2. Transfer max boundary value: 999999999999999; min boundary value: -99999999999999</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K15" s="65" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr">
+      <c r="L15" s="65" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="M15" s="49" t="inlineStr">
+      <c r="M15" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="N15" s="49" t="inlineStr">
+      <c r="N15" s="37" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O15" s="49" t="inlineStr">
+      <c r="O15" s="37" t="inlineStr">
         <is>
           <t>FR-09</t>
         </is>
       </c>
-      <c r="P15" s="49" t="inlineStr">
+      <c r="P15" s="37" t="inlineStr">
         <is>
           <t>@ui @regression @negative @boundary</t>
         </is>
@@ -3223,9 +3434,9 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" style="17" min="7" max="7"/>
+    <col width="26" customWidth="1" style="9" min="7" max="7"/>
     <col width="40.6640625" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" style="17" min="9" max="9"/>
+    <col width="36" customWidth="1" style="9" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
@@ -3235,532 +3446,528 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Scenario ID</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Scenario Name</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="F1" s="20" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="20" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="I1" s="20" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="J1" s="20" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="K1" s="20" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="20" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="20" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>FR Mapping</t>
         </is>
       </c>
-      <c r="N1" s="20" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="O1" s="37" t="n"/>
-    </row>
-    <row r="2" ht="52.8" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="O1" s="28" t="n"/>
+    </row>
+    <row r="2" ht="52.8" customFormat="1" customHeight="1" s="10">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>TC-API-TS03-01</t>
         </is>
       </c>
-      <c r="B2" s="53" t="inlineStr">
+      <c r="B2" s="38" t="inlineStr">
         <is>
           <t>TS-03</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>GET Accounts</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Get All Accounts for Valid Customer</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F2" s="24" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>Verify GET /customers/{customerId}/accounts returns all accounts for a valid customer.</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>User is registered. Customer ID is known.</t>
         </is>
       </c>
-      <c r="H2" s="25" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>1. Send GET /parabank/services/bank/customers/{customerId}/accounts
 2. Set valid customerId</t>
         </is>
       </c>
-      <c r="I2" s="23" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>HTTP 200 OK
 Response is a list of account objects.
 Each account has: id, customerId, type, balance.</t>
         </is>
       </c>
-      <c r="J2" s="22" t="n"/>
-      <c r="K2" s="26" t="inlineStr">
+      <c r="J2" s="13" t="n"/>
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L2" s="22" t="inlineStr">
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M2" s="22" t="inlineStr">
+      <c r="M2" s="13" t="inlineStr">
         <is>
           <t>FR-02</t>
         </is>
       </c>
-      <c r="N2" s="22" t="inlineStr">
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>@api @regression @smoke</t>
         </is>
       </c>
-      <c r="O2" s="22" t="n"/>
+      <c r="O2" s="13" t="n"/>
     </row>
     <row r="3" ht="52.8" customHeight="1">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>TC-API-TS03-02</t>
         </is>
       </c>
-      <c r="B3" s="50" t="n"/>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>GET Accounts</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Get Accounts for Invalid Customer ID</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>Verify API response when an invalid/non-existent customer ID is used.</t>
         </is>
       </c>
-      <c r="G3" s="28" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>API is accessible.</t>
         </is>
       </c>
-      <c r="H3" s="31" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>1. Send GET /parabank/services/bank/customers/9999999/accounts
 2. Use non-existent customerId</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found
 Error message in response body.</t>
         </is>
       </c>
-      <c r="J3" s="52" t="n"/>
-      <c r="K3" s="26" t="inlineStr">
+      <c r="J3" s="37" t="n"/>
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L3" s="52" t="inlineStr">
+      <c r="L3" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="M3" s="52" t="inlineStr">
+      <c r="M3" s="37" t="inlineStr">
         <is>
           <t>FR-02</t>
         </is>
       </c>
-      <c r="N3" s="22" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>@api @regression @negative @smoke</t>
         </is>
       </c>
-      <c r="O3" s="52" t="n"/>
-    </row>
-    <row r="4" ht="39.6" customFormat="1" customHeight="1" s="18">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="O3" s="37" t="n"/>
+    </row>
+    <row r="4" ht="39.6" customFormat="1" customHeight="1" s="10">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>TC-API-TS04-01</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>TS-04</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>API access and response validation</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>GET Account By ID</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Verify GET /accounts/{accountId} returns correct account details.</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Account ID is known.</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>1. Send GET /parabank/services/bank/accounts/{accountId}
 2. Use valid accountId</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>HTTP 200 OK
 Account object returned with correct id, type, balance, customerId.</t>
         </is>
       </c>
-      <c r="J4" s="22" t="n"/>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="J4" s="13" t="n"/>
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L4" s="22" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M4" s="22" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>FR-02</t>
         </is>
       </c>
-      <c r="N4" s="22" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>@api @regression @smoke</t>
         </is>
       </c>
-      <c r="O4" s="22" t="n"/>
+      <c r="O4" s="13" t="n"/>
     </row>
     <row r="5" ht="39.6" customHeight="1">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>TC-API-TS04-02</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n"/>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>API access and response validation</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Get Account with Invalid Account ID</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>Verify API returns 404 for non-existent account ID.</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>API is accessible.</t>
         </is>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>1. Send GET /parabank/services/bank/accounts/0000000
 2. Use invalid accountId</t>
         </is>
       </c>
-      <c r="I5" s="28" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found
 Error message in response body.</t>
         </is>
       </c>
-      <c r="J5" s="52" t="n"/>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="J5" s="37" t="n"/>
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L5" s="52" t="inlineStr">
+      <c r="L5" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="M5" s="52" t="inlineStr">
+      <c r="M5" s="37" t="inlineStr">
         <is>
           <t>FR-02</t>
         </is>
       </c>
-      <c r="N5" s="52" t="inlineStr">
+      <c r="N5" s="37" t="inlineStr">
         <is>
           <t>@api @regression @negative</t>
         </is>
       </c>
-      <c r="O5" s="52" t="n"/>
-    </row>
-    <row r="6" ht="39.6" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="O5" s="37" t="n"/>
+    </row>
+    <row r="6" ht="39.6" customFormat="1" customHeight="1" s="10">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>TC-API-TS06-01</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>TS-06</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>GET Customer</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Get Customer Details by ID</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>Verify GET /customers/{customerId} returns correct customer details.</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>Valid customer ID is known.</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>1. Send GET /parabank/services/bank/customers/{customerId}</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>HTTP 200 OK
 Customer object returned with id, firstName, lastName, address, etc.</t>
         </is>
       </c>
-      <c r="J6" s="22" t="n"/>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>FR-03</t>
         </is>
       </c>
-      <c r="N6" s="22" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>@api @regression @smoke</t>
         </is>
       </c>
-      <c r="O6" s="22" t="n"/>
-    </row>
-    <row r="7" ht="32.4" customFormat="1" customHeight="1" s="18">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="O6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="32.4" customFormat="1" customHeight="1" s="10">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>TC-API-TS06-02</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>TS-06</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>GET Customer</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Get Customer Details by invalidID</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Verify GET /customers/{invalidcustomerId} returns error/null customer details.</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Invalid customer ID is passed.</t>
         </is>
       </c>
-      <c r="H7" s="24" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>1. Send GET /parabank/services/bank/customers/000000</t>
         </is>
       </c>
-      <c r="I7" s="28" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found
 Error message in response body.</t>
         </is>
       </c>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L7" s="22" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="M7" s="22" t="inlineStr">
+      <c r="M7" s="13" t="inlineStr">
         <is>
           <t>FR-03</t>
         </is>
       </c>
-      <c r="N7" s="22" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t>@api @regression @negative @smoke</t>
         </is>
       </c>
-      <c r="O7" s="22" t="n"/>
+      <c r="O7" s="13" t="n"/>
     </row>
     <row r="8" ht="52.8" customHeight="1">
-      <c r="A8" s="52" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>TC-API-TS08-01</t>
         </is>
       </c>
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>TS-08</t>
         </is>
       </c>
-      <c r="C8" s="52" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Performance and Response time</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Login API Response Time</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Verify login API responds within 2 seconds.</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>API is accessible.</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>1. Record start time
 2. Send GET /login/{user}/{pass}
@@ -3768,67 +3975,67 @@
 4. Assert responseTime &lt; 2000ms</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Response completes within 2000ms.</t>
         </is>
       </c>
-      <c r="J8" s="52" t="n"/>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="J8" s="37" t="n"/>
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L8" s="52" t="inlineStr">
+      <c r="L8" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="M8" s="52" t="inlineStr">
+      <c r="M8" s="37" t="inlineStr">
         <is>
           <t>FR-04</t>
         </is>
       </c>
-      <c r="N8" s="22" t="inlineStr">
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>@api @regression @smoke</t>
         </is>
       </c>
-      <c r="O8" s="52" t="n"/>
-    </row>
-    <row r="9" ht="52.8" customFormat="1" customHeight="1" s="18">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="O8" s="37" t="n"/>
+    </row>
+    <row r="9" ht="52.8" customFormat="1" customHeight="1" s="10">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TC-API-TS08-02</t>
         </is>
       </c>
-      <c r="B9" s="50" t="n"/>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Performance and Response time</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Get All Accounts Response Time</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Verify login + get accounts chain responds within 5 seconds.</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Valid customer exists.</t>
         </is>
       </c>
-      <c r="H9" s="24" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>1. Record start time
 2. Login via API
@@ -3836,67 +4043,67 @@
 4. Assert totalTime &lt; 5000ms</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Total chain completes within 5000ms.</t>
         </is>
       </c>
-      <c r="J9" s="22" t="n"/>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>FR-04</t>
         </is>
       </c>
-      <c r="N9" s="22" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>@api @regression</t>
         </is>
       </c>
-      <c r="O9" s="22" t="n"/>
+      <c r="O9" s="13" t="n"/>
     </row>
     <row r="10" ht="66" customHeight="1">
-      <c r="A10" s="52" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>TC-API-TS08-03</t>
         </is>
       </c>
-      <c r="B10" s="48" t="n"/>
-      <c r="C10" s="52" t="inlineStr">
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>Performance and Response time</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>Get Account By ID Response Time</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>Verify login + accounts + accountById chain responds within 5 seconds.</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>Valid account exists.</t>
         </is>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>1. Record start time
 2. Login via API
@@ -3905,383 +4112,384 @@
 5. Assert totalTime &lt; 5000ms</t>
         </is>
       </c>
-      <c r="I10" s="28" t="inlineStr">
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>Total chain completes within 5000ms.</t>
         </is>
       </c>
-      <c r="J10" s="52" t="n"/>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="J10" s="37" t="n"/>
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L10" s="52" t="inlineStr">
+      <c r="L10" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="M10" s="52" t="inlineStr">
+      <c r="M10" s="37" t="inlineStr">
         <is>
           <t>FR-04</t>
         </is>
       </c>
-      <c r="N10" s="22" t="inlineStr">
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>@api @regression @smoke</t>
         </is>
       </c>
-      <c r="O10" s="52" t="n"/>
-    </row>
-    <row r="11" ht="52.8" customFormat="1" customHeight="1" s="18">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="O10" s="37" t="n"/>
+    </row>
+    <row r="11" ht="52.8" customFormat="1" customHeight="1" s="10">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TC-API-TS12-01</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>TS-12</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>GET Transactions</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Get Account Transaction</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>Verify GET /accounts/{accountId}/transactions returns transaction list for one transaction</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Account has at made one transaction.</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>1. Send GET /parabank/services/bank/accounts/{accountId}/transactions</t>
         </is>
       </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>HTTP 200 OK
 List of transaction objects returned.
 Each transaction has: id, accountId, type, date, amount, description.</t>
         </is>
       </c>
-      <c r="J11" s="22" t="n"/>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L11" s="22" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="M11" s="22" t="inlineStr">
+      <c r="M11" s="13" t="inlineStr">
         <is>
           <t>FR-06</t>
         </is>
       </c>
-      <c r="N11" s="22" t="inlineStr">
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t>@api @regression @smoke</t>
         </is>
       </c>
-      <c r="O11" s="22" t="n"/>
-    </row>
-    <row r="12" ht="43.8" customFormat="1" customHeight="1" s="18">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="O11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="43.8" customFormat="1" customHeight="1" s="10">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>TC-API-TS12-02</t>
         </is>
       </c>
-      <c r="B12" s="48" t="n"/>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>GET Transactions</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Get Transactions for Empty Account</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>Verify response when account has no transactions.</t>
         </is>
       </c>
-      <c r="G12" s="34" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>Newly created account with no transactions.</t>
         </is>
       </c>
-      <c r="H12" s="35" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>1. Send GET /accounts/{accountId}/transactions</t>
         </is>
       </c>
-      <c r="I12" s="34" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t>HTTP 200 OK
 Empty array [] returned.</t>
         </is>
       </c>
-      <c r="J12" s="22" t="n"/>
-      <c r="K12" s="26" t="inlineStr">
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t>FR-06</t>
         </is>
       </c>
-      <c r="N12" s="22" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t>@api @regression</t>
         </is>
       </c>
-      <c r="O12" s="22" t="n"/>
+      <c r="O12" s="13" t="n"/>
     </row>
     <row r="13" ht="57.6" customHeight="1">
-      <c r="A13" s="52" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>TC-API-TS14-01</t>
         </is>
       </c>
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>TS-14</t>
         </is>
       </c>
-      <c r="C13" s="52" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Multi-transfer correctness</t>
         </is>
       </c>
-      <c r="D13" s="52" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Validate API after multiple transactions</t>
         </is>
       </c>
-      <c r="E13" s="52" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F13" s="52" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Verify that list of transactions is displayed after multiple transactions</t>
         </is>
       </c>
-      <c r="G13" s="52" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>Successful transfer complete.</t>
         </is>
       </c>
-      <c r="H13" s="36" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>1. Send GET /accounts/{accountId}/transactions</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>HTTP 200 OK
 List of transaction objects returned.
 Each transaction has: id, accountId, type, date, amount, description.</t>
         </is>
       </c>
-      <c r="J13" s="52" t="n"/>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="52" t="inlineStr">
+      <c r="L13" s="37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M13" s="52" t="inlineStr">
+      <c r="M13" s="37" t="inlineStr">
         <is>
           <t>FR-07</t>
         </is>
       </c>
-      <c r="N13" s="52" t="inlineStr">
+      <c r="N13" s="37" t="inlineStr">
         <is>
           <t>@api @regression @smoke</t>
         </is>
       </c>
-      <c r="O13" s="52" t="n"/>
+      <c r="O13" s="37" t="n"/>
     </row>
     <row r="14" ht="26.4" customHeight="1">
-      <c r="A14" s="52" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>TC-API-TS14-02</t>
         </is>
       </c>
-      <c r="B14" s="48" t="n"/>
-      <c r="C14" s="52" t="inlineStr">
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Multi-transfer correctness</t>
         </is>
       </c>
-      <c r="D14" s="52" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Validate the balance</t>
         </is>
       </c>
-      <c r="E14" s="52" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F14" s="52" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Verify the final balance after transaction</t>
         </is>
       </c>
-      <c r="G14" s="52" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>Successful transfer complete.</t>
         </is>
       </c>
-      <c r="H14" s="35" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
         <is>
           <t>1. Send GET /accounts/{newAccountId}/transactions</t>
         </is>
       </c>
-      <c r="I14" s="52" t="inlineStr">
+      <c r="I14" s="37" t="inlineStr">
         <is>
           <t>Exact match.</t>
         </is>
       </c>
-      <c r="J14" s="52" t="n"/>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="J14" s="37" t="n"/>
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="52" t="inlineStr">
+      <c r="L14" s="37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M14" s="52" t="inlineStr">
+      <c r="M14" s="37" t="inlineStr">
         <is>
           <t>FR-07</t>
         </is>
       </c>
-      <c r="N14" s="52" t="inlineStr">
+      <c r="N14" s="37" t="inlineStr">
         <is>
           <t>@api @regression @smoke</t>
         </is>
       </c>
-      <c r="O14" s="52" t="n"/>
+      <c r="O14" s="37" t="n"/>
     </row>
     <row r="15" ht="26.4" customHeight="1">
-      <c r="A15" s="52" t="inlineStr">
-        <is>
-          <t>TC-API-TS18-02</t>
-        </is>
-      </c>
-      <c r="B15" s="52" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>TC-API-TS18-01</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>TS-18</t>
         </is>
       </c>
-      <c r="C15" s="52" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Business-rule and system negatives</t>
         </is>
       </c>
-      <c r="D15" s="52" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Validate API Failure Handling for Unavailable Endpoint</t>
         </is>
       </c>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F15" s="52" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Verify that call account/balance endpoint results in API failure handled correctly.</t>
         </is>
       </c>
-      <c r="G15" s="52" t="inlineStr">
+      <c r="G15" s="37" t="inlineStr">
         <is>
           <t>Invalid or unavailable API.</t>
         </is>
       </c>
-      <c r="H15" s="36" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Call account/balance endpoint.</t>
         </is>
       </c>
-      <c r="I15" s="52" t="inlineStr">
+      <c r="I15" s="37" t="inlineStr">
         <is>
           <t>API failure handled correctly.</t>
         </is>
       </c>
-      <c r="J15" s="52" t="n"/>
-      <c r="K15" s="26" t="inlineStr">
+      <c r="J15" s="37" t="n"/>
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="52" t="inlineStr">
+      <c r="L15" s="37" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="M15" s="52" t="inlineStr">
+      <c r="M15" s="37" t="inlineStr">
         <is>
           <t>FR-09</t>
         </is>
       </c>
-      <c r="N15" s="52" t="inlineStr">
+      <c r="N15" s="37" t="inlineStr">
         <is>
           <t>@api @regression @negative @smoke</t>
         </is>
       </c>
-      <c r="O15" s="52" t="n"/>
+      <c r="O15" s="37" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -4295,283 +4503,284 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.2"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" style="74" min="1" max="1"/>
+    <col width="8" customWidth="1" style="74" min="2" max="2"/>
+    <col width="26" customWidth="1" style="74" min="3" max="3"/>
+    <col width="36" customWidth="1" style="74" min="4" max="4"/>
+    <col width="9" customWidth="1" style="74" min="5" max="5"/>
+    <col width="40" customWidth="1" style="74" min="6" max="6"/>
+    <col width="28" customWidth="1" style="74" min="7" max="7"/>
+    <col width="42" customWidth="1" style="74" min="8" max="8"/>
+    <col width="36" customWidth="1" style="74" min="9" max="9"/>
+    <col width="14" customWidth="1" style="74" min="10" max="10"/>
+    <col width="11" customWidth="1" style="74" min="11" max="11"/>
+    <col width="13" customWidth="1" style="74" min="12" max="12"/>
+    <col width="24" customWidth="1" style="74" min="13" max="13"/>
+    <col width="28" customWidth="1" style="74" min="14" max="14"/>
+    <col width="8.6640625" customWidth="1" style="74" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.8" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="73" t="inlineStr">
         <is>
           <t>Scenario ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="73" t="inlineStr">
         <is>
           <t>Scenario Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="73" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="73" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="73" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="73" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="73" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="73" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="73" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="73" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="73" t="inlineStr">
         <is>
           <t>FR Mapping</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="73" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="73" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
     <row r="2" ht="27.6" customHeight="1">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>TC-E2E-TS05-01</t>
         </is>
       </c>
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>TS-05</t>
         </is>
       </c>
-      <c r="C2" s="49" t="inlineStr">
+      <c r="C2" s="37" t="inlineStr">
         <is>
           <t>UI-created account is present in API</t>
         </is>
       </c>
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="37" t="inlineStr">
         <is>
           <t>Validate UI-Created Account ID via API</t>
         </is>
       </c>
-      <c r="E2" s="49" t="inlineStr">
+      <c r="E2" s="37" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="F2" s="49" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Verify that capture UI account ID results in matching account is present in API response.</t>
         </is>
       </c>
-      <c r="G2" s="49" t="inlineStr">
+      <c r="G2" s="37" t="inlineStr">
         <is>
           <t>Account created successfully via UI.</t>
         </is>
       </c>
-      <c r="H2" s="49" t="inlineStr">
+      <c r="H2" s="37" t="inlineStr">
         <is>
           <t>Capture UI account ID; call GET accounts; search for ID.</t>
         </is>
       </c>
-      <c r="I2" s="49" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
         <is>
           <t>Matching account is present in API response.</t>
         </is>
       </c>
-      <c r="J2" s="49" t="n"/>
-      <c r="K2" s="13" t="inlineStr">
+      <c r="J2" s="37" t="n"/>
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L2" s="49" t="inlineStr">
+      <c r="L2" s="37" t="inlineStr">
         <is>
           <t>FR-03</t>
         </is>
       </c>
-      <c r="M2" s="49" t="inlineStr">
+      <c r="M2" s="37" t="inlineStr">
         <is>
           <t>@hybrid @e2e @regression @smoke</t>
         </is>
       </c>
-      <c r="N2" s="49" t="n"/>
+      <c r="N2" s="37" t="n"/>
     </row>
     <row r="3" ht="41.4" customHeight="1">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>TC-E2E-TS05-02</t>
         </is>
       </c>
-      <c r="B3" s="48" t="n"/>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="B3" s="35" t="n"/>
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>UI-created account is present in API</t>
         </is>
       </c>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="D3" s="37" t="inlineStr">
         <is>
           <t>Validate UI Account Name Matches API Payload</t>
         </is>
       </c>
-      <c r="E3" s="49" t="inlineStr">
+      <c r="E3" s="37" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="F3" s="49" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Verify that compare UI account name with API payload results in API contains the same account record.</t>
         </is>
       </c>
-      <c r="G3" s="49" t="inlineStr">
+      <c r="G3" s="37" t="inlineStr">
         <is>
           <t>Same as above.</t>
         </is>
       </c>
-      <c r="H3" s="49" t="inlineStr">
+      <c r="H3" s="37" t="inlineStr">
         <is>
           <t>Compare UI account name with API payload.</t>
         </is>
       </c>
-      <c r="I3" s="49" t="inlineStr">
+      <c r="I3" s="37" t="inlineStr">
         <is>
           <t>API contains the same account record.</t>
         </is>
       </c>
-      <c r="J3" s="49" t="n"/>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="J3" s="37" t="n"/>
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L3" s="49" t="inlineStr">
+      <c r="L3" s="37" t="inlineStr">
         <is>
           <t>FR-03</t>
         </is>
       </c>
-      <c r="M3" s="49" t="inlineStr">
+      <c r="M3" s="37" t="inlineStr">
         <is>
           <t>@hybrid @e2e @regression</t>
         </is>
       </c>
-      <c r="N3" s="49" t="n"/>
+      <c r="N3" s="37" t="n"/>
     </row>
     <row r="4" ht="27.6" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>TC-E2E-TS07-01</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr">
+      <c r="B4" s="57" t="inlineStr">
         <is>
           <t>TS-07</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>Type and details match UI</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Validate Account Type Matches Between UI and API</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Verify that note account type in UI results in account type matches exactly.</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="37" t="inlineStr">
         <is>
           <t>Account created via UI.</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="37" t="inlineStr">
         <is>
           <t>Note account type in UI; fetch API record; compare type.</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
         <is>
           <t>Account type matches exactly.</t>
         </is>
       </c>
-      <c r="J4" s="49" t="n"/>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="J4" s="37" t="n"/>
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="L4" s="37" t="inlineStr">
         <is>
           <t>FR-04</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="37" t="inlineStr">
         <is>
           <t>@hybrid @e2e @regression @smoke</t>
         </is>
       </c>
-      <c r="N4" s="49" t="n"/>
+      <c r="N4" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4583,280 +4792,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Requirement Description</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenarios</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case IDs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>TC Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="27.6" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
-        <is>
-          <t>FR-01</t>
-        </is>
-      </c>
-      <c r="B2" s="47" t="inlineStr">
-        <is>
-          <t>Create new account via UI</t>
-        </is>
-      </c>
-      <c r="C2" s="49" t="inlineStr">
-        <is>
-          <t>TS-01, TS-02</t>
-        </is>
-      </c>
-      <c r="D2" s="49" t="inlineStr">
-        <is>
-          <t>TC-FR01-TS01-01, TC-FR01-TS01-02, TC-FR01-TS01-03, TC-FR01-TS02-01, TC-FR01-TS02-02, TC-FR01-TS02-03</t>
-        </is>
-      </c>
-      <c r="E2" s="49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="27.6" customHeight="1">
-      <c r="A3" s="47" t="inlineStr">
-        <is>
-          <t>FR-02</t>
-        </is>
-      </c>
-      <c r="B3" s="47" t="inlineStr">
-        <is>
-          <t>GET accounts list via API</t>
-        </is>
-      </c>
-      <c r="C3" s="49" t="inlineStr">
-        <is>
-          <t>TS-03, TS-04</t>
-        </is>
-      </c>
-      <c r="D3" s="49" t="inlineStr">
-        <is>
-          <t>TC-FR02-TS03-01, TC-FR02-TS03-02, TC-FR02-TS03-03, TC-FR02-TS04-01, TC-FR02-TS04-02, TC-FR02-TS04-03</t>
-        </is>
-      </c>
-      <c r="E3" s="49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" ht="27.6" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
-        <is>
-          <t>FR-03</t>
-        </is>
-      </c>
-      <c r="B4" s="47" t="inlineStr">
-        <is>
-          <t>Validate new account exists in API</t>
-        </is>
-      </c>
-      <c r="C4" s="49" t="inlineStr">
-        <is>
-          <t>TS-05, TS-06</t>
-        </is>
-      </c>
-      <c r="D4" s="49" t="inlineStr">
-        <is>
-          <t>TC-FR03-TS05-01, TC-FR03-TS05-02, TC-FR03-TS05-03, TC-FR03-TS06-01, TC-FR03-TS06-02, TC-FR03-TS06-03</t>
-        </is>
-      </c>
-      <c r="E4" s="49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" ht="27.6" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
-        <is>
-          <t>FR-04</t>
-        </is>
-      </c>
-      <c r="B5" s="47" t="inlineStr">
-        <is>
-          <t>Validate account type and details in API</t>
-        </is>
-      </c>
-      <c r="C5" s="49" t="inlineStr">
-        <is>
-          <t>TS-07, TS-08</t>
-        </is>
-      </c>
-      <c r="D5" s="49" t="inlineStr">
-        <is>
-          <t>TC-FR04-TS07-01, TC-FR04-TS07-02, TC-FR04-TS07-03, TC-FR04-TS08-01, TC-FR04-TS08-02, TC-FR04-TS08-03</t>
-        </is>
-      </c>
-      <c r="E5" s="49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" ht="27.6" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
-        <is>
-          <t>FR-05</t>
-        </is>
-      </c>
-      <c r="B6" s="47" t="inlineStr">
-        <is>
-          <t>Transfer funds via UI</t>
-        </is>
-      </c>
-      <c r="C6" s="49" t="inlineStr">
-        <is>
-          <t>TS-09, TS-10</t>
-        </is>
-      </c>
-      <c r="D6" s="49" t="inlineStr">
-        <is>
-          <t>TC-FR05-TS09-01, TC-FR05-TS09-02, TC-FR05-TS09-03, TC-FR05-TS10-01, TC-FR05-TS10-02, TC-FR05-TS10-03</t>
-        </is>
-      </c>
-      <c r="E6" s="49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" ht="27.6" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t>FR-06</t>
-        </is>
-      </c>
-      <c r="B7" s="47" t="inlineStr">
-        <is>
-          <t>Validate updated balances using API</t>
-        </is>
-      </c>
-      <c r="C7" s="49" t="inlineStr">
-        <is>
-          <t>TS-11, TS-12</t>
-        </is>
-      </c>
-      <c r="D7" s="49" t="inlineStr">
-        <is>
-          <t>TC-FR06-TS11-01, TC-FR06-TS11-02, TC-FR06-TS11-03, TC-FR06-TS12-01, TC-FR06-TS12-02, TC-FR06-TS12-03</t>
-        </is>
-      </c>
-      <c r="E7" s="49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" ht="27.6" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
-        <is>
-          <t>FR-07</t>
-        </is>
-      </c>
-      <c r="B8" s="47" t="inlineStr">
-        <is>
-          <t>Validate transfer applied correctly (before/after values)</t>
-        </is>
-      </c>
-      <c r="C8" s="49" t="inlineStr">
-        <is>
-          <t>TS-13, TS-14</t>
-        </is>
-      </c>
-      <c r="D8" s="49" t="inlineStr">
-        <is>
-          <t>TC-FR07-TS13-01, TC-FR07-TS13-02, TC-FR07-TS13-03, TC-FR07-TS14-01, TC-FR07-TS14-02, TC-FR07-TS14-03</t>
-        </is>
-      </c>
-      <c r="E8" s="49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" ht="27.6" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
-        <is>
-          <t>FR-08</t>
-        </is>
-      </c>
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t>Validate UI messages (success, confirmation)</t>
-        </is>
-      </c>
-      <c r="C9" s="49" t="inlineStr">
-        <is>
-          <t>TS-15, TS-16</t>
-        </is>
-      </c>
-      <c r="D9" s="49" t="inlineStr">
-        <is>
-          <t>TC-FR08-TS15-01, TC-FR08-TS15-02, TC-FR08-TS15-03, TC-FR08-TS16-01, TC-FR08-TS16-02, TC-FR08-TS16-03</t>
-        </is>
-      </c>
-      <c r="E9" s="49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" ht="27.6" customHeight="1">
-      <c r="A10" s="47" t="inlineStr">
-        <is>
-          <t>FR-09</t>
-        </is>
-      </c>
-      <c r="B10" s="47" t="inlineStr">
-        <is>
-          <t>Validate negative scenarios</t>
-        </is>
-      </c>
-      <c r="C10" s="49" t="inlineStr">
-        <is>
-          <t>TS-17, TS-18</t>
-        </is>
-      </c>
-      <c r="D10" s="49" t="inlineStr">
-        <is>
-          <t>TC-FR09-TS17-01, TC-FR09-TS17-02, TC-FR09-TS17-03, TC-FR09-TS18-01, TC-FR09-TS18-02, TC-FR09-TS18-03</t>
-        </is>
-      </c>
-      <c r="E10" s="49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4956,23 +4891,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="7" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -4980,1880 +4914,1880 @@
   </cols>
   <sheetData>
     <row r="1" ht="34.5" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>TEST EXECUTION REPORT — ParaBank Capstone</t>
         </is>
       </c>
-      <c r="B1" s="57" t="n"/>
-      <c r="C1" s="57" t="n"/>
-      <c r="D1" s="57" t="n"/>
-      <c r="E1" s="57" t="n"/>
-      <c r="F1" s="57" t="n"/>
-      <c r="G1" s="57" t="n"/>
-      <c r="H1" s="57" t="n"/>
-      <c r="I1" s="57" t="n"/>
-      <c r="J1" s="57" t="n"/>
-      <c r="K1" s="57" t="n"/>
-      <c r="L1" s="57" t="n"/>
+      <c r="B1" s="86" t="n"/>
+      <c r="C1" s="86" t="n"/>
+      <c r="D1" s="86" t="n"/>
+      <c r="E1" s="86" t="n"/>
+      <c r="F1" s="86" t="n"/>
+      <c r="G1" s="86" t="n"/>
+      <c r="H1" s="86" t="n"/>
+      <c r="I1" s="86" t="n"/>
+      <c r="J1" s="86" t="n"/>
+      <c r="K1" s="86" t="n"/>
+      <c r="L1" s="87" t="n"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B2" s="58" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>Scenario ID</t>
         </is>
       </c>
-      <c r="C2" s="58" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D2" s="58" t="inlineStr">
+      <c r="D2" s="29" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
       </c>
-      <c r="E2" s="58" t="inlineStr">
+      <c r="E2" s="29" t="inlineStr">
         <is>
           <t>Executed By</t>
         </is>
       </c>
-      <c r="F2" s="58" t="inlineStr">
+      <c r="F2" s="29" t="inlineStr">
         <is>
           <t>Exec Date</t>
         </is>
       </c>
-      <c r="G2" s="58" t="inlineStr">
+      <c r="G2" s="29" t="inlineStr">
         <is>
           <t>Browser</t>
         </is>
       </c>
-      <c r="H2" s="58" t="inlineStr">
+      <c r="H2" s="29" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I2" s="58" t="inlineStr">
+      <c r="I2" s="29" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="J2" s="58" t="inlineStr">
+      <c r="J2" s="29" t="inlineStr">
         <is>
           <t>Defect ID</t>
         </is>
       </c>
-      <c r="K2" s="58" t="inlineStr">
+      <c r="K2" s="29" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="L2" s="58" t="inlineStr">
+      <c r="L2" s="29" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS01-01</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>TS-01</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="51" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="D3" s="60" t="inlineStr">
+      <c r="D3" s="52" t="inlineStr">
         <is>
           <t>Register new account</t>
         </is>
       </c>
-      <c r="E3" s="61" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F3" s="61" t="n"/>
-      <c r="G3" s="59" t="inlineStr">
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H3" s="62" t="inlineStr">
+      <c r="H3" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I3" s="60" t="inlineStr">
+      <c r="I3" s="52" t="inlineStr">
         <is>
           <t>Account registration successful, account is valid for 30 mins</t>
         </is>
       </c>
-      <c r="J3" s="59" t="inlineStr">
+      <c r="J3" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K3" s="61" t="inlineStr">
+      <c r="K3" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L3" s="60" t="inlineStr">
+      <c r="L3" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS01-02</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>TS-01</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="52" t="inlineStr">
         <is>
           <t>Login with valid credentials</t>
         </is>
       </c>
-      <c r="E4" s="61" t="inlineStr">
+      <c r="E4" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F4" s="61" t="n"/>
-      <c r="G4" s="59" t="inlineStr">
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H4" s="62" t="inlineStr">
+      <c r="H4" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="52" t="inlineStr">
         <is>
           <t>Account login is successful with valid credentials</t>
         </is>
       </c>
-      <c r="J4" s="59" t="inlineStr">
+      <c r="J4" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K4" s="61" t="inlineStr">
+      <c r="K4" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L4" s="60" t="inlineStr">
+      <c r="L4" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS01-03</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>TS-01</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
+      <c r="D5" s="52" t="inlineStr">
         <is>
           <t>Login with invalid credentials</t>
         </is>
       </c>
-      <c r="E5" s="61" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F5" s="61" t="n"/>
-      <c r="G5" s="59" t="inlineStr">
+      <c r="F5" s="53" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H5" s="62" t="inlineStr">
+      <c r="H5" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="52" t="inlineStr">
         <is>
           <t>Invalid credentials not found; login unsuccessful</t>
         </is>
       </c>
-      <c r="J5" s="59" t="inlineStr">
+      <c r="J5" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="61" t="inlineStr">
+      <c r="K5" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L5" s="60" t="inlineStr">
+      <c r="L5" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS01-04</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>TS-01</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="D6" s="52" t="inlineStr">
         <is>
           <t>Savings account</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F6" s="61" t="n"/>
-      <c r="G6" s="59" t="inlineStr">
+      <c r="F6" s="53" t="n"/>
+      <c r="G6" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H6" s="62" t="inlineStr">
+      <c r="H6" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="52" t="inlineStr">
         <is>
           <t>New savings account opened for the registered user</t>
         </is>
       </c>
-      <c r="J6" s="59" t="inlineStr">
+      <c r="J6" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="61" t="inlineStr">
+      <c r="K6" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L6" s="60" t="inlineStr">
+      <c r="L6" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS02-01</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="51" t="inlineStr">
         <is>
           <t>TS-02</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D7" s="60" t="inlineStr">
+      <c r="D7" s="52" t="inlineStr">
         <is>
           <t>Account Creation with Blank Username</t>
         </is>
       </c>
-      <c r="E7" s="61" t="inlineStr">
+      <c r="E7" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F7" s="61" t="n"/>
-      <c r="G7" s="59" t="inlineStr">
+      <c r="F7" s="53" t="n"/>
+      <c r="G7" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H7" s="62" t="inlineStr">
+      <c r="H7" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="52" t="inlineStr">
         <is>
           <t>Account registration without username unsuccessful</t>
         </is>
       </c>
-      <c r="J7" s="59" t="inlineStr">
+      <c r="J7" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="61" t="inlineStr">
+      <c r="K7" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L7" s="60" t="inlineStr">
+      <c r="L7" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="31.5" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS02-03</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="51" t="inlineStr">
         <is>
           <t>TS-02</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D8" s="60" t="inlineStr">
+      <c r="D8" s="52" t="inlineStr">
         <is>
           <t>Account Creation with mismatched password</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr">
+      <c r="E8" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F8" s="61" t="n"/>
-      <c r="G8" s="59" t="inlineStr">
+      <c r="F8" s="53" t="n"/>
+      <c r="G8" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H8" s="62" t="inlineStr">
+      <c r="H8" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="52" t="inlineStr">
         <is>
           <t>Password did not match error</t>
         </is>
       </c>
-      <c r="J8" s="59" t="inlineStr">
+      <c r="J8" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="61" t="inlineStr">
+      <c r="K8" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L8" s="60" t="inlineStr">
+      <c r="L8" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS09-01</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="51" t="inlineStr">
         <is>
           <t>TS-09</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="D9" s="52" t="inlineStr">
         <is>
           <t>Transfer Valid Amount Between Own Accounts</t>
         </is>
       </c>
-      <c r="E9" s="61" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F9" s="61" t="n"/>
-      <c r="G9" s="59" t="inlineStr">
+      <c r="F9" s="53" t="n"/>
+      <c r="G9" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H9" s="62" t="inlineStr">
+      <c r="H9" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="52" t="inlineStr">
         <is>
           <t>1. Funds transferred successfully. Message 'Transfer Complete!' displayed with the correct amount.
 2. Transfer happens only to self account (Saving and/or Checking type account)</t>
         </is>
       </c>
-      <c r="J9" s="59" t="inlineStr">
+      <c r="J9" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="61" t="inlineStr">
+      <c r="K9" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L9" s="60" t="inlineStr">
+      <c r="L9" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="31.5" customHeight="1">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS09-02</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="51" t="inlineStr">
         <is>
           <t>TS-09</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="51" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="52" t="inlineStr">
         <is>
           <t>Transfer Minimum Valid Amount</t>
         </is>
       </c>
-      <c r="E10" s="61" t="inlineStr">
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F10" s="61" t="n"/>
-      <c r="G10" s="59" t="inlineStr">
+      <c r="F10" s="53" t="n"/>
+      <c r="G10" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H10" s="63" t="inlineStr">
+      <c r="H10" s="55" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="52" t="inlineStr">
         <is>
           <t>Transaction is successful even if typed negative values</t>
         </is>
       </c>
-      <c r="J10" s="59" t="inlineStr">
+      <c r="J10" s="51" t="inlineStr">
         <is>
           <t>DEF-01</t>
         </is>
       </c>
-      <c r="K10" s="61" t="inlineStr">
+      <c r="K10" s="53" t="inlineStr">
         <is>
           <t>Screenshot + trace</t>
         </is>
       </c>
-      <c r="L10" s="60" t="inlineStr">
+      <c r="L10" s="52" t="inlineStr">
         <is>
           <t>Transfer of negative values allowed without validation</t>
         </is>
       </c>
     </row>
     <row r="11" ht="31.5" customHeight="1">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS09-03</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="51" t="inlineStr">
         <is>
           <t>TS-09</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="51" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
+      <c r="D11" s="52" t="inlineStr">
         <is>
           <t>Transfer to a Valid Destination Account</t>
         </is>
       </c>
-      <c r="E11" s="61" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F11" s="61" t="n"/>
-      <c r="G11" s="59" t="inlineStr">
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H11" s="62" t="inlineStr">
+      <c r="H11" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="52" t="inlineStr">
         <is>
           <t>Successful transaction transfer to valid different destination account</t>
         </is>
       </c>
-      <c r="J11" s="59" t="inlineStr">
+      <c r="J11" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K11" s="61" t="inlineStr">
+      <c r="K11" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L11" s="60" t="inlineStr">
+      <c r="L11" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="31.5" customHeight="1">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS10-01</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="51" t="inlineStr">
         <is>
           <t>TS-10</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr">
+      <c r="D12" s="52" t="inlineStr">
         <is>
           <t>Transfer Amount Exceeding Source Balance</t>
         </is>
       </c>
-      <c r="E12" s="61" t="inlineStr">
+      <c r="E12" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F12" s="61" t="n"/>
-      <c r="G12" s="59" t="inlineStr">
+      <c r="F12" s="53" t="n"/>
+      <c r="G12" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H12" s="63" t="inlineStr">
+      <c r="H12" s="55" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="52" t="inlineStr">
         <is>
           <t>Transaction successful even when exceeding amount is applied</t>
         </is>
       </c>
-      <c r="J12" s="59" t="inlineStr">
+      <c r="J12" s="51" t="inlineStr">
         <is>
           <t>DEF-02</t>
         </is>
       </c>
-      <c r="K12" s="61" t="inlineStr">
+      <c r="K12" s="53" t="inlineStr">
         <is>
           <t>Screenshot + trace</t>
         </is>
       </c>
-      <c r="L12" s="60" t="inlineStr">
+      <c r="L12" s="52" t="inlineStr">
         <is>
           <t>Overdraft allowed; transfer exceeding available balance accepted</t>
         </is>
       </c>
     </row>
     <row r="13" ht="31.5" customHeight="1">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS10-02</t>
         </is>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="51" t="inlineStr">
         <is>
           <t>TS-10</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr">
+      <c r="D13" s="52" t="inlineStr">
         <is>
           <t>Transfer with Invalid Destination Account Number</t>
         </is>
       </c>
-      <c r="E13" s="61" t="inlineStr">
+      <c r="E13" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F13" s="61" t="n"/>
-      <c r="G13" s="59" t="inlineStr">
+      <c r="F13" s="53" t="n"/>
+      <c r="G13" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H13" s="62" t="inlineStr">
+      <c r="H13" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="52" t="inlineStr">
         <is>
           <t>Invalid destination account number is not visible i.e. the destination account does not exist</t>
         </is>
       </c>
-      <c r="J13" s="59" t="inlineStr">
+      <c r="J13" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K13" s="61" t="inlineStr">
+      <c r="K13" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L13" s="60" t="inlineStr">
+      <c r="L13" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="31.5" customHeight="1">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS15-01</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="51" t="inlineStr">
         <is>
           <t>TS-15</t>
         </is>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="51" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="52" t="inlineStr">
         <is>
           <t>Verify Success Message on Account Creation</t>
         </is>
       </c>
-      <c r="E14" s="61" t="inlineStr">
+      <c r="E14" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F14" s="61" t="n"/>
-      <c r="G14" s="59" t="inlineStr">
+      <c r="F14" s="53" t="n"/>
+      <c r="G14" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H14" s="62" t="inlineStr">
+      <c r="H14" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="I14" s="52" t="inlineStr">
         <is>
           <t>Validation message is visible after successful account creation</t>
         </is>
       </c>
-      <c r="J14" s="59" t="inlineStr">
+      <c r="J14" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K14" s="61" t="inlineStr">
+      <c r="K14" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L14" s="60" t="inlineStr">
+      <c r="L14" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15" ht="31.5" customHeight="1">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS16-01</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="51" t="inlineStr">
         <is>
           <t>TS-16</t>
         </is>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D15" s="60" t="inlineStr">
+      <c r="D15" s="52" t="inlineStr">
         <is>
           <t>Verify Error Message Shown Instead of Confirmation</t>
         </is>
       </c>
-      <c r="E15" s="61" t="inlineStr">
+      <c r="E15" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F15" s="61" t="n"/>
-      <c r="G15" s="59" t="inlineStr">
+      <c r="F15" s="53" t="n"/>
+      <c r="G15" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H15" s="62" t="inlineStr">
+      <c r="H15" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="I15" s="52" t="inlineStr">
         <is>
           <t>Error message displayed on entering non-numeric value</t>
         </is>
       </c>
-      <c r="J15" s="59" t="inlineStr">
+      <c r="J15" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="61" t="inlineStr">
+      <c r="K15" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L15" s="60" t="inlineStr">
+      <c r="L15" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16" ht="31.5" customHeight="1">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>TC-UI-TS17-01</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="51" t="inlineStr">
         <is>
           <t>TS-17</t>
         </is>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr">
+      <c r="D16" s="52" t="inlineStr">
         <is>
           <t>Submit Form with Boundary-Breaking Values</t>
         </is>
       </c>
-      <c r="E16" s="61" t="inlineStr">
+      <c r="E16" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F16" s="61" t="n"/>
-      <c r="G16" s="59" t="inlineStr">
+      <c r="F16" s="53" t="n"/>
+      <c r="G16" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H16" s="64" t="inlineStr">
+      <c r="H16" s="56" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I16" s="52" t="inlineStr">
         <is>
           <t>1. No boundary value or out-of-range values are present for input fields of registration
 2. Transfer max boundary value: 999999999999999; min boundary value: -99999999999999</t>
         </is>
       </c>
-      <c r="J16" s="59" t="inlineStr">
+      <c r="J16" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K16" s="61" t="inlineStr">
+      <c r="K16" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L16" s="60" t="inlineStr">
+      <c r="L16" s="52" t="inlineStr">
         <is>
           <t>Boundary value constraints not defined on input fields</t>
         </is>
       </c>
     </row>
     <row r="17" ht="31.5" customHeight="1">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS03-01</t>
         </is>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="51" t="inlineStr">
         <is>
           <t>TS-03</t>
         </is>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D17" s="52" t="inlineStr">
         <is>
           <t>Get All Accounts for Valid Customer</t>
         </is>
       </c>
-      <c r="E17" s="61" t="inlineStr">
+      <c r="E17" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F17" s="61" t="n"/>
-      <c r="G17" s="59" t="inlineStr">
+      <c r="F17" s="53" t="n"/>
+      <c r="G17" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H17" s="62" t="inlineStr">
+      <c r="H17" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I17" s="52" t="inlineStr">
         <is>
           <t>HTTP 200 OK. Returned list of account objects with correct fields.</t>
         </is>
       </c>
-      <c r="J17" s="59" t="inlineStr">
+      <c r="J17" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K17" s="61" t="inlineStr">
+      <c r="K17" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L17" s="60" t="inlineStr">
+      <c r="L17" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18" ht="31.5" customHeight="1">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS03-02</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B18" s="51" t="inlineStr">
         <is>
           <t>TS-03</t>
         </is>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr">
+      <c r="D18" s="52" t="inlineStr">
         <is>
           <t>Get Accounts for Invalid Customer ID</t>
         </is>
       </c>
-      <c r="E18" s="61" t="inlineStr">
+      <c r="E18" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F18" s="61" t="n"/>
-      <c r="G18" s="59" t="inlineStr">
+      <c r="F18" s="53" t="n"/>
+      <c r="G18" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H18" s="62" t="inlineStr">
+      <c r="H18" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="52" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found. Error message returned in response body.</t>
         </is>
       </c>
-      <c r="J18" s="59" t="inlineStr">
+      <c r="J18" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K18" s="61" t="inlineStr">
+      <c r="K18" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L18" s="60" t="inlineStr">
+      <c r="L18" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19" ht="31.5" customHeight="1">
-      <c r="A19" s="59" t="inlineStr">
+      <c r="A19" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS04-01</t>
         </is>
       </c>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="51" t="inlineStr">
         <is>
           <t>TS-04</t>
         </is>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr">
+      <c r="D19" s="52" t="inlineStr">
         <is>
           <t>GET Account By ID</t>
         </is>
       </c>
-      <c r="E19" s="61" t="inlineStr">
+      <c r="E19" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F19" s="61" t="n"/>
-      <c r="G19" s="59" t="inlineStr">
+      <c r="F19" s="53" t="n"/>
+      <c r="G19" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H19" s="62" t="inlineStr">
+      <c r="H19" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I19" s="60" t="inlineStr">
+      <c r="I19" s="52" t="inlineStr">
         <is>
           <t>HTTP 200 OK. Account object returned with correct details.</t>
         </is>
       </c>
-      <c r="J19" s="59" t="inlineStr">
+      <c r="J19" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="61" t="inlineStr">
+      <c r="K19" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L19" s="60" t="inlineStr">
+      <c r="L19" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="31.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS04-02</t>
         </is>
       </c>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>TS-04</t>
         </is>
       </c>
-      <c r="C20" s="59" t="inlineStr">
+      <c r="C20" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr">
+      <c r="D20" s="52" t="inlineStr">
         <is>
           <t>Get Account with Invalid Account ID</t>
         </is>
       </c>
-      <c r="E20" s="61" t="inlineStr">
+      <c r="E20" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F20" s="61" t="n"/>
-      <c r="G20" s="59" t="inlineStr">
+      <c r="F20" s="53" t="n"/>
+      <c r="G20" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H20" s="62" t="inlineStr">
+      <c r="H20" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I20" s="60" t="inlineStr">
+      <c r="I20" s="52" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found. Error message returned in response body.</t>
         </is>
       </c>
-      <c r="J20" s="59" t="inlineStr">
+      <c r="J20" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K20" s="61" t="inlineStr">
+      <c r="K20" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L20" s="60" t="inlineStr">
+      <c r="L20" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="21" ht="31.5" customHeight="1">
-      <c r="A21" s="59" t="inlineStr">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS06-01</t>
         </is>
       </c>
-      <c r="B21" s="59" t="inlineStr">
+      <c r="B21" s="51" t="inlineStr">
         <is>
           <t>TS-06</t>
         </is>
       </c>
-      <c r="C21" s="59" t="inlineStr">
+      <c r="C21" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr">
+      <c r="D21" s="52" t="inlineStr">
         <is>
           <t>Get Customer Details by ID</t>
         </is>
       </c>
-      <c r="E21" s="61" t="inlineStr">
+      <c r="E21" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F21" s="61" t="n"/>
-      <c r="G21" s="59" t="inlineStr">
+      <c r="F21" s="53" t="n"/>
+      <c r="G21" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H21" s="62" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I21" s="60" t="inlineStr">
+      <c r="I21" s="52" t="inlineStr">
         <is>
           <t>HTTP 200 OK. Customer details returned successfully.</t>
         </is>
       </c>
-      <c r="J21" s="59" t="inlineStr">
+      <c r="J21" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K21" s="61" t="inlineStr">
+      <c r="K21" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L21" s="60" t="inlineStr">
+      <c r="L21" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="31.5" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS06-02</t>
         </is>
       </c>
-      <c r="B22" s="59" t="inlineStr">
+      <c r="B22" s="51" t="inlineStr">
         <is>
           <t>TS-06</t>
         </is>
       </c>
-      <c r="C22" s="59" t="inlineStr">
+      <c r="C22" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D22" s="60" t="inlineStr">
+      <c r="D22" s="52" t="inlineStr">
         <is>
           <t>Get Customer Details by invalidID</t>
         </is>
       </c>
-      <c r="E22" s="61" t="inlineStr">
+      <c r="E22" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F22" s="61" t="n"/>
-      <c r="G22" s="59" t="inlineStr">
+      <c r="F22" s="53" t="n"/>
+      <c r="G22" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H22" s="62" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I22" s="60" t="inlineStr">
+      <c r="I22" s="52" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found. Error message returned in response body.</t>
         </is>
       </c>
-      <c r="J22" s="59" t="inlineStr">
+      <c r="J22" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K22" s="61" t="inlineStr">
+      <c r="K22" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L22" s="60" t="inlineStr">
+      <c r="L22" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="23" ht="31.5" customHeight="1">
-      <c r="A23" s="59" t="inlineStr">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS08-01</t>
         </is>
       </c>
-      <c r="B23" s="59" t="inlineStr">
+      <c r="B23" s="51" t="inlineStr">
         <is>
           <t>TS-08</t>
         </is>
       </c>
-      <c r="C23" s="59" t="inlineStr">
+      <c r="C23" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="60" t="inlineStr">
+      <c r="D23" s="52" t="inlineStr">
         <is>
           <t>Login API Response Time</t>
         </is>
       </c>
-      <c r="E23" s="61" t="inlineStr">
+      <c r="E23" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F23" s="61" t="n"/>
-      <c r="G23" s="59" t="inlineStr">
+      <c r="F23" s="53" t="n"/>
+      <c r="G23" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H23" s="62" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I23" s="60" t="inlineStr">
+      <c r="I23" s="52" t="inlineStr">
         <is>
           <t>Response completed successfully within 2000ms.</t>
         </is>
       </c>
-      <c r="J23" s="59" t="inlineStr">
+      <c r="J23" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K23" s="61" t="inlineStr">
+      <c r="K23" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L23" s="60" t="inlineStr">
+      <c r="L23" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="24" ht="31.5" customHeight="1">
-      <c r="A24" s="59" t="inlineStr">
+      <c r="A24" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS08-02</t>
         </is>
       </c>
-      <c r="B24" s="59" t="inlineStr">
+      <c r="B24" s="51" t="inlineStr">
         <is>
           <t>TS-08</t>
         </is>
       </c>
-      <c r="C24" s="59" t="inlineStr">
+      <c r="C24" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D24" s="60" t="inlineStr">
+      <c r="D24" s="52" t="inlineStr">
         <is>
           <t>Get All Accounts Response Time</t>
         </is>
       </c>
-      <c r="E24" s="61" t="inlineStr">
+      <c r="E24" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F24" s="61" t="n"/>
-      <c r="G24" s="59" t="inlineStr">
+      <c r="F24" s="53" t="n"/>
+      <c r="G24" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H24" s="62" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I24" s="60" t="inlineStr">
+      <c r="I24" s="52" t="inlineStr">
         <is>
           <t>Login + get accounts chain completed within 5000ms.</t>
         </is>
       </c>
-      <c r="J24" s="59" t="inlineStr">
+      <c r="J24" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K24" s="61" t="inlineStr">
+      <c r="K24" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L24" s="60" t="inlineStr">
+      <c r="L24" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="25" ht="31.5" customHeight="1">
-      <c r="A25" s="59" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS08-03</t>
         </is>
       </c>
-      <c r="B25" s="59" t="inlineStr">
+      <c r="B25" s="51" t="inlineStr">
         <is>
           <t>TS-08</t>
         </is>
       </c>
-      <c r="C25" s="59" t="inlineStr">
+      <c r="C25" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D25" s="60" t="inlineStr">
+      <c r="D25" s="52" t="inlineStr">
         <is>
           <t>Get Account By ID Response Time</t>
         </is>
       </c>
-      <c r="E25" s="61" t="inlineStr">
+      <c r="E25" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F25" s="61" t="n"/>
-      <c r="G25" s="59" t="inlineStr">
+      <c r="F25" s="53" t="n"/>
+      <c r="G25" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H25" s="62" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I25" s="60" t="inlineStr">
+      <c r="I25" s="52" t="inlineStr">
         <is>
           <t>Login + accounts + accountById chain completed within 5000ms.</t>
         </is>
       </c>
-      <c r="J25" s="59" t="inlineStr">
+      <c r="J25" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K25" s="61" t="inlineStr">
+      <c r="K25" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L25" s="60" t="inlineStr">
+      <c r="L25" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="26" ht="31.5" customHeight="1">
-      <c r="A26" s="59" t="inlineStr">
+      <c r="A26" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS12-01</t>
         </is>
       </c>
-      <c r="B26" s="59" t="inlineStr">
+      <c r="B26" s="51" t="inlineStr">
         <is>
           <t>TS-12</t>
         </is>
       </c>
-      <c r="C26" s="59" t="inlineStr">
+      <c r="C26" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D26" s="60" t="inlineStr">
+      <c r="D26" s="52" t="inlineStr">
         <is>
           <t>Get Account Transaction</t>
         </is>
       </c>
-      <c r="E26" s="61" t="inlineStr">
+      <c r="E26" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F26" s="61" t="n"/>
-      <c r="G26" s="59" t="inlineStr">
+      <c r="F26" s="53" t="n"/>
+      <c r="G26" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H26" s="62" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I26" s="60" t="inlineStr">
+      <c r="I26" s="52" t="inlineStr">
         <is>
           <t>HTTP 200 OK. Returned transaction list for the account.</t>
         </is>
       </c>
-      <c r="J26" s="59" t="inlineStr">
+      <c r="J26" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K26" s="61" t="inlineStr">
+      <c r="K26" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L26" s="60" t="inlineStr">
+      <c r="L26" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27" ht="31.5" customHeight="1">
-      <c r="A27" s="59" t="inlineStr">
+      <c r="A27" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS12-02</t>
         </is>
       </c>
-      <c r="B27" s="59" t="inlineStr">
+      <c r="B27" s="51" t="inlineStr">
         <is>
           <t>TS-12</t>
         </is>
       </c>
-      <c r="C27" s="59" t="inlineStr">
+      <c r="C27" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D27" s="60" t="inlineStr">
+      <c r="D27" s="52" t="inlineStr">
         <is>
           <t>Get Transactions for Empty Account</t>
         </is>
       </c>
-      <c r="E27" s="61" t="inlineStr">
+      <c r="E27" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F27" s="61" t="n"/>
-      <c r="G27" s="59" t="inlineStr">
+      <c r="F27" s="53" t="n"/>
+      <c r="G27" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H27" s="62" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I27" s="60" t="inlineStr">
+      <c r="I27" s="52" t="inlineStr">
         <is>
           <t>HTTP 200 OK. Empty array [] returned for account with no transactions.</t>
         </is>
       </c>
-      <c r="J27" s="59" t="inlineStr">
+      <c r="J27" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K27" s="61" t="inlineStr">
+      <c r="K27" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L27" s="60" t="inlineStr">
+      <c r="L27" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="28" ht="31.5" customHeight="1">
-      <c r="A28" s="59" t="inlineStr">
+      <c r="A28" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS14-01</t>
         </is>
       </c>
-      <c r="B28" s="59" t="inlineStr">
+      <c r="B28" s="51" t="inlineStr">
         <is>
           <t>TS-14</t>
         </is>
       </c>
-      <c r="C28" s="59" t="inlineStr">
+      <c r="C28" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D28" s="60" t="inlineStr">
+      <c r="D28" s="52" t="inlineStr">
         <is>
           <t>Validate API after multiple transactions</t>
         </is>
       </c>
-      <c r="E28" s="61" t="inlineStr">
+      <c r="E28" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F28" s="61" t="n"/>
-      <c r="G28" s="59" t="inlineStr">
+      <c r="F28" s="53" t="n"/>
+      <c r="G28" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H28" s="62" t="inlineStr">
+      <c r="H28" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I28" s="60" t="inlineStr">
+      <c r="I28" s="52" t="inlineStr">
         <is>
           <t>HTTP 200 OK. List of transaction objects returned after multiple transactions.</t>
         </is>
       </c>
-      <c r="J28" s="59" t="inlineStr">
+      <c r="J28" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K28" s="61" t="inlineStr">
+      <c r="K28" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L28" s="60" t="inlineStr">
+      <c r="L28" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="29" ht="31.5" customHeight="1">
-      <c r="A29" s="59" t="inlineStr">
+      <c r="A29" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS14-02</t>
         </is>
       </c>
-      <c r="B29" s="59" t="inlineStr">
+      <c r="B29" s="51" t="inlineStr">
         <is>
           <t>TS-14</t>
         </is>
       </c>
-      <c r="C29" s="59" t="inlineStr">
+      <c r="C29" s="51" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D29" s="60" t="inlineStr">
+      <c r="D29" s="52" t="inlineStr">
         <is>
           <t>Validate the balance</t>
         </is>
       </c>
-      <c r="E29" s="61" t="inlineStr">
+      <c r="E29" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F29" s="61" t="n"/>
-      <c r="G29" s="59" t="inlineStr">
+      <c r="F29" s="53" t="n"/>
+      <c r="G29" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H29" s="62" t="inlineStr">
+      <c r="H29" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I29" s="60" t="inlineStr">
+      <c r="I29" s="52" t="inlineStr">
         <is>
           <t>Exact match of final balance after transaction.</t>
         </is>
       </c>
-      <c r="J29" s="59" t="inlineStr">
+      <c r="J29" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K29" s="61" t="inlineStr">
+      <c r="K29" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L29" s="60" t="inlineStr">
+      <c r="L29" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="30" ht="31.5" customHeight="1">
-      <c r="A30" s="59" t="inlineStr">
+      <c r="A30" s="51" t="inlineStr">
         <is>
           <t>TC-API-TS18-02</t>
         </is>
       </c>
-      <c r="B30" s="59" t="inlineStr">
+      <c r="B30" s="51" t="inlineStr">
         <is>
           <t>TS-18</t>
         </is>
       </c>
-      <c r="C30" s="59" t="inlineStr">
+      <c r="C30" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D30" s="60" t="inlineStr">
+      <c r="D30" s="52" t="inlineStr">
         <is>
           <t>Validate API Failure Handling for Unavailable Endpoint</t>
         </is>
       </c>
-      <c r="E30" s="61" t="inlineStr">
+      <c r="E30" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F30" s="61" t="n"/>
-      <c r="G30" s="59" t="inlineStr">
+      <c r="F30" s="53" t="n"/>
+      <c r="G30" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H30" s="62" t="inlineStr">
+      <c r="H30" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I30" s="60" t="inlineStr">
+      <c r="I30" s="52" t="inlineStr">
         <is>
           <t>API failure handled correctly for unavailable endpoint.</t>
         </is>
       </c>
-      <c r="J30" s="59" t="inlineStr">
+      <c r="J30" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K30" s="61" t="inlineStr">
+      <c r="K30" s="53" t="inlineStr">
         <is>
           <t>JSON log</t>
         </is>
       </c>
-      <c r="L30" s="60" t="inlineStr">
+      <c r="L30" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="31" ht="31.5" customHeight="1">
-      <c r="A31" s="59" t="inlineStr">
+      <c r="A31" s="51" t="inlineStr">
         <is>
           <t>TC-E2E-TS05-01</t>
         </is>
       </c>
-      <c r="B31" s="59" t="inlineStr">
+      <c r="B31" s="51" t="inlineStr">
         <is>
           <t>TS-05</t>
         </is>
       </c>
-      <c r="C31" s="59" t="inlineStr">
+      <c r="C31" s="51" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="D31" s="60" t="inlineStr">
+      <c r="D31" s="52" t="inlineStr">
         <is>
           <t>Validate UI-Created Account ID via API</t>
         </is>
       </c>
-      <c r="E31" s="61" t="inlineStr">
+      <c r="E31" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F31" s="61" t="n"/>
-      <c r="G31" s="59" t="inlineStr">
+      <c r="F31" s="53" t="n"/>
+      <c r="G31" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H31" s="62" t="inlineStr">
+      <c r="H31" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I31" s="60" t="inlineStr">
+      <c r="I31" s="52" t="inlineStr">
         <is>
           <t>Matching account was successfully verified in API response.</t>
         </is>
       </c>
-      <c r="J31" s="59" t="inlineStr">
+      <c r="J31" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K31" s="61" t="inlineStr">
+      <c r="K31" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L31" s="60" t="inlineStr">
+      <c r="L31" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="32" ht="31.5" customHeight="1">
-      <c r="A32" s="59" t="inlineStr">
+      <c r="A32" s="51" t="inlineStr">
         <is>
           <t>TC-E2E-TS05-02</t>
         </is>
       </c>
-      <c r="B32" s="59" t="inlineStr">
+      <c r="B32" s="51" t="inlineStr">
         <is>
           <t>TS-05</t>
         </is>
       </c>
-      <c r="C32" s="59" t="inlineStr">
+      <c r="C32" s="51" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="D32" s="60" t="inlineStr">
+      <c r="D32" s="52" t="inlineStr">
         <is>
           <t>Validate UI Account Name Matches API Payload</t>
         </is>
       </c>
-      <c r="E32" s="61" t="inlineStr">
+      <c r="E32" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F32" s="61" t="n"/>
-      <c r="G32" s="59" t="inlineStr">
+      <c r="F32" s="53" t="n"/>
+      <c r="G32" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H32" s="62" t="inlineStr">
+      <c r="H32" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I32" s="60" t="inlineStr">
+      <c r="I32" s="52" t="inlineStr">
         <is>
           <t>Verified that UI account name matches API payload record.</t>
         </is>
       </c>
-      <c r="J32" s="59" t="inlineStr">
+      <c r="J32" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K32" s="61" t="inlineStr">
+      <c r="K32" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L32" s="60" t="inlineStr">
+      <c r="L32" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="33" ht="31.5" customHeight="1">
-      <c r="A33" s="59" t="inlineStr">
+      <c r="A33" s="51" t="inlineStr">
         <is>
           <t>TC-E2E-TS07-01</t>
         </is>
       </c>
-      <c r="B33" s="59" t="inlineStr">
+      <c r="B33" s="51" t="inlineStr">
         <is>
           <t>TS-07</t>
         </is>
       </c>
-      <c r="C33" s="59" t="inlineStr">
+      <c r="C33" s="51" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="D33" s="60" t="inlineStr">
+      <c r="D33" s="52" t="inlineStr">
         <is>
           <t>Validate Account Type Matches Between UI and API</t>
         </is>
       </c>
-      <c r="E33" s="61" t="inlineStr">
+      <c r="E33" s="53" t="inlineStr">
         <is>
           <t>Bhavraj Sairem</t>
         </is>
       </c>
-      <c r="F33" s="61" t="n"/>
-      <c r="G33" s="59" t="inlineStr">
+      <c r="F33" s="53" t="n"/>
+      <c r="G33" s="51" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="H33" s="62" t="inlineStr">
+      <c r="H33" s="54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I33" s="60" t="inlineStr">
+      <c r="I33" s="52" t="inlineStr">
         <is>
           <t>Account type matched exactly between UI and API.</t>
         </is>
       </c>
-      <c r="J33" s="59" t="inlineStr">
+      <c r="J33" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K33" s="61" t="inlineStr">
+      <c r="K33" s="53" t="inlineStr">
         <is>
           <t>Allure + trace</t>
         </is>
       </c>
-      <c r="L33" s="60" t="inlineStr">
+      <c r="L33" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6861,89 +6795,82 @@
     </row>
     <row r="34" ht="15" customHeight="1"/>
     <row r="35" ht="21.75" customHeight="1">
-      <c r="A35" s="65" t="inlineStr">
+      <c r="A35" s="49" t="inlineStr">
         <is>
           <t>EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B35" s="66" t="n"/>
-      <c r="C35" s="66" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="67" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>Total Test Cases Executed</t>
         </is>
       </c>
-      <c r="B36" s="68" t="n">
+      <c r="B36" s="47" t="n">
         <v>31</v>
       </c>
-      <c r="C36" s="69" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="67" t="inlineStr">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="B37" s="70" t="n">
+      <c r="B37" s="43" t="n">
         <v>28</v>
       </c>
-      <c r="C37" s="71" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="B38" s="72" t="n">
+      <c r="B38" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="73" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="67" t="inlineStr">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="B39" s="74" t="n">
+      <c r="B39" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="75" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="67" t="inlineStr">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>Defects Logged</t>
         </is>
       </c>
-      <c r="B40" s="68" t="inlineStr">
+      <c r="B40" s="47" t="inlineStr">
         <is>
           <t>2 (DEF-01 to DEF-02)</t>
         </is>
       </c>
-      <c r="C40" s="69" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1"/>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="76" t="inlineStr">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>STATUS LEGEND →</t>
         </is>
       </c>
-      <c r="B42" s="77" t="inlineStr">
+      <c r="B42" s="32" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C42" s="78" t="inlineStr">
+      <c r="C42" s="33" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D42" s="79" t="inlineStr">
+      <c r="D42" s="34" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -6961,4 +6888,360 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34.5" customHeight="1">
+      <c r="A1" s="88" t="inlineStr">
+        <is>
+          <t>REQUIREMENT TRACEABILITY MATRIX (RTM)</t>
+        </is>
+      </c>
+      <c r="B1" s="89" t="n"/>
+      <c r="C1" s="89" t="n"/>
+      <c r="D1" s="89" t="n"/>
+      <c r="E1" s="89" t="n"/>
+      <c r="F1" s="89" t="n"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
+      <c r="A2" s="90" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B2" s="90" t="inlineStr">
+        <is>
+          <t>Requirement Description</t>
+        </is>
+      </c>
+      <c r="C2" s="90" t="inlineStr">
+        <is>
+          <t>Test Scenario(s)</t>
+        </is>
+      </c>
+      <c r="D2" s="90" t="inlineStr">
+        <is>
+          <t>Test Case(s)</t>
+        </is>
+      </c>
+      <c r="E2" s="90" t="inlineStr">
+        <is>
+          <t># TCs</t>
+        </is>
+      </c>
+      <c r="F2" s="90" t="inlineStr">
+        <is>
+          <t>Coverage Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="43.5" customHeight="1">
+      <c r="A3" s="91" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="B3" s="92" t="inlineStr">
+        <is>
+          <t>Create new account via UI</t>
+        </is>
+      </c>
+      <c r="C3" s="92" t="inlineStr">
+        <is>
+          <t>TS-01, TS-02</t>
+        </is>
+      </c>
+      <c r="D3" s="92" t="inlineStr">
+        <is>
+          <t>TC-UI-TS01-01, TC-UI-TS01-02, TC-UI-TS01-03, TC-UI-TS01-04, TC-UI-TS02-01, TC-UI-TS02-03</t>
+        </is>
+      </c>
+      <c r="E3" s="91" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="93" t="inlineStr">
+        <is>
+          <t>✅ Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="43.5" customHeight="1">
+      <c r="A4" s="91" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="B4" s="92" t="inlineStr">
+        <is>
+          <t>GET accounts list via API</t>
+        </is>
+      </c>
+      <c r="C4" s="92" t="inlineStr">
+        <is>
+          <t>TS-03, TS-04</t>
+        </is>
+      </c>
+      <c r="D4" s="92" t="inlineStr">
+        <is>
+          <t>TC-API-TS03-01, TC-API-TS03-02, TC-API-TS04-01, TC-API-TS04-02</t>
+        </is>
+      </c>
+      <c r="E4" s="91" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="93" t="inlineStr">
+        <is>
+          <t>✅ Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="43.5" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="B5" s="92" t="inlineStr">
+        <is>
+          <t>Validate new account exists in API</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>TS-05, TS-06</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>TC-API-TS06-01, TC-API-TS06-02, TC-E2E-TS05-01, TC-E2E-TS05-02</t>
+        </is>
+      </c>
+      <c r="E5" s="91" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="93" t="inlineStr">
+        <is>
+          <t>✅ Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="43.5" customHeight="1">
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t>FR-04</t>
+        </is>
+      </c>
+      <c r="B6" s="92" t="inlineStr">
+        <is>
+          <t>Validate account type and details in API</t>
+        </is>
+      </c>
+      <c r="C6" s="92" t="inlineStr">
+        <is>
+          <t>TS-07, TS-08</t>
+        </is>
+      </c>
+      <c r="D6" s="92" t="inlineStr">
+        <is>
+          <t>TC-API-TS08-01, TC-API-TS08-02, TC-API-TS08-03, TC-E2E-TS07-01</t>
+        </is>
+      </c>
+      <c r="E6" s="91" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="93" t="inlineStr">
+        <is>
+          <t>✅ Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="43.5" customHeight="1">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>FR-05</t>
+        </is>
+      </c>
+      <c r="B7" s="92" t="inlineStr">
+        <is>
+          <t>Transfer funds via UI</t>
+        </is>
+      </c>
+      <c r="C7" s="92" t="inlineStr">
+        <is>
+          <t>TS-09, TS-10</t>
+        </is>
+      </c>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>TC-UI-TS09-01, TC-UI-TS09-02, TC-UI-TS09-03, TC-UI-TS10-01, TC-UI-TS10-02</t>
+        </is>
+      </c>
+      <c r="E7" s="91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="93" t="inlineStr">
+        <is>
+          <t>✅ Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="43.5" customHeight="1">
+      <c r="A8" s="91" t="inlineStr">
+        <is>
+          <t>FR-06</t>
+        </is>
+      </c>
+      <c r="B8" s="92" t="inlineStr">
+        <is>
+          <t>Validate updated balances using API</t>
+        </is>
+      </c>
+      <c r="C8" s="92" t="inlineStr">
+        <is>
+          <t>TS-11, TS-12</t>
+        </is>
+      </c>
+      <c r="D8" s="92" t="inlineStr">
+        <is>
+          <t>TC-API-TS12-01, TC-API-TS12-02</t>
+        </is>
+      </c>
+      <c r="E8" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="93" t="inlineStr">
+        <is>
+          <t>✅ Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="43.5" customHeight="1">
+      <c r="A9" s="91" t="inlineStr">
+        <is>
+          <t>FR-07</t>
+        </is>
+      </c>
+      <c r="B9" s="92" t="inlineStr">
+        <is>
+          <t>Validate transfer applied correctly (before/after values)</t>
+        </is>
+      </c>
+      <c r="C9" s="92" t="inlineStr">
+        <is>
+          <t>TS-13, TS-14</t>
+        </is>
+      </c>
+      <c r="D9" s="92" t="inlineStr">
+        <is>
+          <t>TC-API-TS14-01, TC-API-TS14-02</t>
+        </is>
+      </c>
+      <c r="E9" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="93" t="inlineStr">
+        <is>
+          <t>✅ Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="43.5" customHeight="1">
+      <c r="A10" s="91" t="inlineStr">
+        <is>
+          <t>FR-08</t>
+        </is>
+      </c>
+      <c r="B10" s="92" t="inlineStr">
+        <is>
+          <t>Validate UI messages (success, confirmation)</t>
+        </is>
+      </c>
+      <c r="C10" s="92" t="inlineStr">
+        <is>
+          <t>TS-15, TS-16</t>
+        </is>
+      </c>
+      <c r="D10" s="92" t="inlineStr">
+        <is>
+          <t>TC-UI-TS15-01, TC-UI-TS16-01</t>
+        </is>
+      </c>
+      <c r="E10" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="93" t="inlineStr">
+        <is>
+          <t>✅ Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="43.5" customHeight="1">
+      <c r="A11" s="91" t="inlineStr">
+        <is>
+          <t>FR-09</t>
+        </is>
+      </c>
+      <c r="B11" s="92" t="inlineStr">
+        <is>
+          <t>Validate negative scenarios</t>
+        </is>
+      </c>
+      <c r="C11" s="92" t="inlineStr">
+        <is>
+          <t>TS-17, TS-18</t>
+        </is>
+      </c>
+      <c r="D11" s="92" t="inlineStr">
+        <is>
+          <t>TC-API-TS18-01, TC-UI-TS17-01</t>
+        </is>
+      </c>
+      <c r="E11" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="93" t="inlineStr">
+        <is>
+          <t>✅ Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="43.5" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t>TOTAL: 9 Requirements | 31 Test Cases | ALL COVERED</t>
+        </is>
+      </c>
+      <c r="B12" s="95" t="n"/>
+      <c r="C12" s="95" t="n"/>
+      <c r="D12" s="95" t="n"/>
+      <c r="E12" s="95" t="n"/>
+      <c r="F12" s="96" t="inlineStr">
+        <is>
+          <t>✅ 100%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>